--- a/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_FRA_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3999D6CB-FE17-417D-BD03-6A707AB5B119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A72B32D-39A2-4794-B454-9A1D55C6AEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -732,12 +732,6 @@
     <t>S1aH1,S4aH3,S2aH1,S3aH3,S4aH1,S1aH3,S2aH3,S3aH1</t>
   </si>
   <si>
-    <t>elc_buildings</t>
-  </si>
-  <si>
-    <t>elc_industry</t>
-  </si>
-  <si>
     <t>com_pkflx</t>
   </si>
   <si>
@@ -751,6 +745,12 @@
   </si>
   <si>
     <t>hydro</t>
+  </si>
+  <si>
+    <t>*[_]buildings</t>
+  </si>
+  <si>
+    <t>*[_]industry</t>
   </si>
 </sst>
 </file>
@@ -20709,6 +20709,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6831029-69F7-412B-B65A-C9262ED3EA6F}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="8" max="8" width="12.1328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="9" spans="1:19" x14ac:dyDescent="0.45">
       <c r="C9" t="str">
@@ -20716,8 +20719,8 @@
         <v>~TFM_DINS-AT</v>
       </c>
       <c r="H9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>~TFM_DINS-AT</v>
+        <f>IF(A11="x","DeActivated","~TFM_INS-AT: cset_set=DEM")</f>
+        <v>~TFM_INS-AT: cset_set=DEM</v>
       </c>
       <c r="L9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
@@ -20760,19 +20763,19 @@
         <v>48</v>
       </c>
       <c r="N10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="P10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Q10" t="s">
         <v>48</v>
       </c>
       <c r="R10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="S10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.45">
@@ -20793,7 +20796,7 @@
         <v>224</v>
       </c>
       <c r="H11" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I11" t="s">
         <v>52</v>
@@ -20820,7 +20823,7 @@
         <v>0.31556666666666672</v>
       </c>
       <c r="S11" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.45">
@@ -20837,7 +20840,7 @@
         <v>224</v>
       </c>
       <c r="H12" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I12" t="s">
         <v>54</v>
@@ -20864,7 +20867,7 @@
         <v>0.32903333333333334</v>
       </c>
       <c r="S12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.45">
@@ -20881,7 +20884,7 @@
         <v>224</v>
       </c>
       <c r="H13" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I13" t="s">
         <v>55</v>
@@ -20908,7 +20911,7 @@
         <v>0.2475333333333333</v>
       </c>
       <c r="S13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.45">
@@ -20925,7 +20928,7 @@
         <v>224</v>
       </c>
       <c r="H14" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I14" t="s">
         <v>56</v>
@@ -20952,7 +20955,7 @@
         <v>0.21636666666666668</v>
       </c>
       <c r="S14" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.45">
@@ -20969,7 +20972,7 @@
         <v>224</v>
       </c>
       <c r="H15" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I15" t="s">
         <v>57</v>
@@ -20996,7 +20999,7 @@
         <v>0.33883333333333332</v>
       </c>
       <c r="S15" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.45">
@@ -21013,7 +21016,7 @@
         <v>224</v>
       </c>
       <c r="H16" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I16" t="s">
         <v>58</v>
@@ -21040,7 +21043,7 @@
         <v>0.27746666666666669</v>
       </c>
       <c r="S16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" spans="3:19" x14ac:dyDescent="0.45">
@@ -21057,7 +21060,7 @@
         <v>224</v>
       </c>
       <c r="H17" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I17" t="s">
         <v>59</v>
@@ -21084,7 +21087,7 @@
         <v>0.27649999999999997</v>
       </c>
       <c r="S17" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.45">
@@ -21101,7 +21104,7 @@
         <v>224</v>
       </c>
       <c r="H18" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I18" t="s">
         <v>60</v>
@@ -21128,7 +21131,7 @@
         <v>0.17016666666666666</v>
       </c>
       <c r="S18" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.45">
@@ -21145,7 +21148,7 @@
         <v>224</v>
       </c>
       <c r="H19" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I19" t="s">
         <v>61</v>
@@ -21172,7 +21175,7 @@
         <v>0.25390000000000001</v>
       </c>
       <c r="S19" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.45">
@@ -21189,7 +21192,7 @@
         <v>224</v>
       </c>
       <c r="H20" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I20" t="s">
         <v>62</v>
@@ -21216,7 +21219,7 @@
         <v>0.23780000000000001</v>
       </c>
       <c r="S20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.45">
@@ -21233,7 +21236,7 @@
         <v>224</v>
       </c>
       <c r="H21" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I21" t="s">
         <v>63</v>
@@ -21260,7 +21263,7 @@
         <v>0.16893333333333335</v>
       </c>
       <c r="S21" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22" spans="3:19" x14ac:dyDescent="0.45">
@@ -21277,7 +21280,7 @@
         <v>224</v>
       </c>
       <c r="H22" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I22" t="s">
         <v>64</v>
@@ -21304,12 +21307,12 @@
         <v>0.15003333333333332</v>
       </c>
       <c r="S22" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H23" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I23" t="s">
         <v>52</v>
@@ -21327,12 +21330,12 @@
         <v>0.29619999999999996</v>
       </c>
       <c r="S23" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H24" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I24" t="s">
         <v>54</v>
@@ -21350,12 +21353,12 @@
         <v>0.27356666666666668</v>
       </c>
       <c r="S24" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H25" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I25" t="s">
         <v>55</v>
@@ -21373,12 +21376,12 @@
         <v>0.23003333333333331</v>
       </c>
       <c r="S25" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H26" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I26" t="s">
         <v>56</v>
@@ -21396,12 +21399,12 @@
         <v>0.2056</v>
       </c>
       <c r="S26" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H27" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I27" t="s">
         <v>57</v>
@@ -21419,12 +21422,12 @@
         <v>0.30990000000000001</v>
       </c>
       <c r="S27" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H28" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I28" t="s">
         <v>58</v>
@@ -21442,12 +21445,12 @@
         <v>0.24750000000000003</v>
       </c>
       <c r="S28" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H29" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I29" t="s">
         <v>59</v>
@@ -21465,12 +21468,12 @@
         <v>0.23356666666666667</v>
       </c>
       <c r="S29" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H30" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I30" t="s">
         <v>60</v>
@@ -21488,12 +21491,12 @@
         <v>0.18826666666666667</v>
       </c>
       <c r="S30" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H31" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I31" t="s">
         <v>61</v>
@@ -21511,12 +21514,12 @@
         <v>0.30763333333333337</v>
       </c>
       <c r="S31" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H32" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I32" t="s">
         <v>62</v>
@@ -21534,12 +21537,12 @@
         <v>0.32896666666666668</v>
       </c>
       <c r="S32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H33" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I33" t="s">
         <v>63</v>
@@ -21557,12 +21560,12 @@
         <v>0.23676666666666665</v>
       </c>
       <c r="S33" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H34" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I34" t="s">
         <v>64</v>
@@ -21580,7 +21583,7 @@
         <v>0.20086666666666667</v>
       </c>
       <c r="S34" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" spans="8:19" x14ac:dyDescent="0.45">
@@ -21594,7 +21597,7 @@
         <v>0.3652333333333333</v>
       </c>
       <c r="S35" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="36" spans="8:19" x14ac:dyDescent="0.45">
@@ -21608,7 +21611,7 @@
         <v>0.34646666666666665</v>
       </c>
       <c r="S36" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37" spans="8:19" x14ac:dyDescent="0.45">
@@ -21622,7 +21625,7 @@
         <v>0.25796666666666668</v>
       </c>
       <c r="S37" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="38" spans="8:19" x14ac:dyDescent="0.45">
@@ -21636,7 +21639,7 @@
         <v>0.19089999999999999</v>
       </c>
       <c r="S38" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39" spans="8:19" x14ac:dyDescent="0.45">
@@ -21650,7 +21653,7 @@
         <v>0.31886666666666663</v>
       </c>
       <c r="S39" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="40" spans="8:19" x14ac:dyDescent="0.45">
@@ -21664,7 +21667,7 @@
         <v>0.34953333333333331</v>
       </c>
       <c r="S40" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="41" spans="8:19" x14ac:dyDescent="0.45">
@@ -21678,7 +21681,7 @@
         <v>0.24443333333333331</v>
       </c>
       <c r="S41" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="42" spans="8:19" x14ac:dyDescent="0.45">
@@ -21692,7 +21695,7 @@
         <v>0.16983333333333331</v>
       </c>
       <c r="S42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43" spans="8:19" x14ac:dyDescent="0.45">
@@ -21706,7 +21709,7 @@
         <v>0.31743333333333335</v>
       </c>
       <c r="S43" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="44" spans="8:19" x14ac:dyDescent="0.45">
@@ -21720,7 +21723,7 @@
         <v>0.36359999999999992</v>
       </c>
       <c r="S44" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="45" spans="8:19" x14ac:dyDescent="0.45">
@@ -21734,7 +21737,7 @@
         <v>0.24803333333333333</v>
       </c>
       <c r="S45" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46" spans="8:19" x14ac:dyDescent="0.45">
@@ -21748,7 +21751,7 @@
         <v>0.20230000000000001</v>
       </c>
       <c r="S46" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="47" spans="8:19" x14ac:dyDescent="0.45">
@@ -21762,7 +21765,7 @@
         <v>0.33770000000000006</v>
       </c>
       <c r="S47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" spans="8:19" x14ac:dyDescent="0.45">
@@ -21776,7 +21779,7 @@
         <v>0.34693333333333332</v>
       </c>
       <c r="S48" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49" spans="16:19" x14ac:dyDescent="0.45">
@@ -21790,7 +21793,7 @@
         <v>0.2714333333333333</v>
       </c>
       <c r="S49" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50" spans="16:19" x14ac:dyDescent="0.45">
@@ -21804,7 +21807,7 @@
         <v>0.20003333333333337</v>
       </c>
       <c r="S50" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" spans="16:19" x14ac:dyDescent="0.45">
@@ -21818,7 +21821,7 @@
         <v>0.2742</v>
       </c>
       <c r="S51" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="52" spans="16:19" x14ac:dyDescent="0.45">
@@ -21832,7 +21835,7 @@
         <v>0.25089999999999996</v>
       </c>
       <c r="S52" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53" spans="16:19" x14ac:dyDescent="0.45">
@@ -21846,7 +21849,7 @@
         <v>0.23026666666666665</v>
       </c>
       <c r="S53" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="54" spans="16:19" x14ac:dyDescent="0.45">
@@ -21860,7 +21863,7 @@
         <v>0.18776666666666667</v>
       </c>
       <c r="S54" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" spans="16:19" x14ac:dyDescent="0.45">
@@ -21874,7 +21877,7 @@
         <v>0.30149999999999993</v>
       </c>
       <c r="S55" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="16:19" x14ac:dyDescent="0.45">
@@ -21888,7 +21891,7 @@
         <v>0.33426666666666666</v>
       </c>
       <c r="S56" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="57" spans="16:19" x14ac:dyDescent="0.45">
@@ -21902,7 +21905,7 @@
         <v>0.25666666666666665</v>
       </c>
       <c r="S57" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="58" spans="16:19" x14ac:dyDescent="0.45">
@@ -21916,7 +21919,7 @@
         <v>0.17489999999999997</v>
       </c>
       <c r="S58" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="59" spans="16:19" x14ac:dyDescent="0.45">
@@ -21930,7 +21933,7 @@
         <v>0.27499999999999997</v>
       </c>
       <c r="S59" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="60" spans="16:19" x14ac:dyDescent="0.45">
@@ -21944,7 +21947,7 @@
         <v>0.27550000000000002</v>
       </c>
       <c r="S60" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="61" spans="16:19" x14ac:dyDescent="0.45">
@@ -21958,7 +21961,7 @@
         <v>0.23386666666666667</v>
       </c>
       <c r="S61" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="62" spans="16:19" x14ac:dyDescent="0.45">
@@ -21972,7 +21975,7 @@
         <v>0.15140000000000001</v>
       </c>
       <c r="S62" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="63" spans="16:19" x14ac:dyDescent="0.45">
@@ -21986,7 +21989,7 @@
         <v>0.28456666666666669</v>
       </c>
       <c r="S63" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="64" spans="16:19" x14ac:dyDescent="0.45">
@@ -22000,7 +22003,7 @@
         <v>0.33493333333333331</v>
       </c>
       <c r="S64" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="65" spans="16:19" x14ac:dyDescent="0.45">
@@ -22014,7 +22017,7 @@
         <v>0.25253333333333333</v>
       </c>
       <c r="S65" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="66" spans="16:19" x14ac:dyDescent="0.45">
@@ -22028,7 +22031,7 @@
         <v>0.17956666666666665</v>
       </c>
       <c r="S66" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="67" spans="16:19" x14ac:dyDescent="0.45">
@@ -22042,7 +22045,7 @@
         <v>0.28899999999999998</v>
       </c>
       <c r="S67" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="68" spans="16:19" x14ac:dyDescent="0.45">
@@ -22056,7 +22059,7 @@
         <v>0.29876666666666668</v>
       </c>
       <c r="S68" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" spans="16:19" x14ac:dyDescent="0.45">
@@ -22070,7 +22073,7 @@
         <v>0.24546666666666669</v>
       </c>
       <c r="S69" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="70" spans="16:19" x14ac:dyDescent="0.45">
@@ -22084,7 +22087,7 @@
         <v>0.1855</v>
       </c>
       <c r="S70" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="71" spans="16:19" x14ac:dyDescent="0.45">
@@ -22098,7 +22101,7 @@
         <v>0.27283333333333332</v>
       </c>
       <c r="S71" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72" spans="16:19" x14ac:dyDescent="0.45">
@@ -22112,7 +22115,7 @@
         <v>0.27016666666666667</v>
       </c>
       <c r="S72" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="73" spans="16:19" x14ac:dyDescent="0.45">
@@ -22126,7 +22129,7 @@
         <v>0.20276666666666668</v>
       </c>
       <c r="S73" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="74" spans="16:19" x14ac:dyDescent="0.45">
@@ -22140,7 +22143,7 @@
         <v>0.1724</v>
       </c>
       <c r="S74" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="75" spans="16:19" x14ac:dyDescent="0.45">
@@ -22154,7 +22157,7 @@
         <v>0.31776666666666664</v>
       </c>
       <c r="S75" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="76" spans="16:19" x14ac:dyDescent="0.45">
@@ -22168,7 +22171,7 @@
         <v>0.29699999999999999</v>
       </c>
       <c r="S76" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" spans="16:19" x14ac:dyDescent="0.45">
@@ -22182,7 +22185,7 @@
         <v>0.23066666666666669</v>
       </c>
       <c r="S77" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="78" spans="16:19" x14ac:dyDescent="0.45">
@@ -22196,7 +22199,7 @@
         <v>0.17943333333333333</v>
       </c>
       <c r="S78" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="79" spans="16:19" x14ac:dyDescent="0.45">
@@ -22210,7 +22213,7 @@
         <v>0.3617333333333333</v>
       </c>
       <c r="S79" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="80" spans="16:19" x14ac:dyDescent="0.45">
@@ -22224,7 +22227,7 @@
         <v>0.29273333333333335</v>
       </c>
       <c r="S80" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="81" spans="16:19" x14ac:dyDescent="0.45">
@@ -22238,7 +22241,7 @@
         <v>0.25616666666666665</v>
       </c>
       <c r="S81" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="82" spans="16:19" x14ac:dyDescent="0.45">
@@ -22252,7 +22255,7 @@
         <v>0.20813333333333331</v>
       </c>
       <c r="S82" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="83" spans="16:19" x14ac:dyDescent="0.45">
@@ -22266,7 +22269,7 @@
         <v>0.38593333333333329</v>
       </c>
       <c r="S83" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="84" spans="16:19" x14ac:dyDescent="0.45">
@@ -22280,7 +22283,7 @@
         <v>0.36663333333333331</v>
       </c>
       <c r="S84" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="85" spans="16:19" x14ac:dyDescent="0.45">
@@ -22294,7 +22297,7 @@
         <v>0.28786666666666666</v>
       </c>
       <c r="S85" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="86" spans="16:19" x14ac:dyDescent="0.45">
@@ -22308,7 +22311,7 @@
         <v>0.23529999999999998</v>
       </c>
       <c r="S86" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="87" spans="16:19" x14ac:dyDescent="0.45">
@@ -22322,7 +22325,7 @@
         <v>0.37480000000000002</v>
       </c>
       <c r="S87" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="88" spans="16:19" x14ac:dyDescent="0.45">
@@ -22336,7 +22339,7 @@
         <v>0.34139999999999998</v>
       </c>
       <c r="S88" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="89" spans="16:19" x14ac:dyDescent="0.45">
@@ -22350,7 +22353,7 @@
         <v>0.2883</v>
       </c>
       <c r="S89" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="90" spans="16:19" x14ac:dyDescent="0.45">
@@ -22364,7 +22367,7 @@
         <v>0.28793333333333332</v>
       </c>
       <c r="S90" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="91" spans="16:19" x14ac:dyDescent="0.45">
@@ -22378,7 +22381,7 @@
         <v>0.41136666666666666</v>
       </c>
       <c r="S91" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="92" spans="16:19" x14ac:dyDescent="0.45">
@@ -22392,7 +22395,7 @@
         <v>0.40083333333333332</v>
       </c>
       <c r="S92" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="93" spans="16:19" x14ac:dyDescent="0.45">
@@ -22406,7 +22409,7 @@
         <v>0.31986666666666669</v>
       </c>
       <c r="S93" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="94" spans="16:19" x14ac:dyDescent="0.45">
@@ -22420,7 +22423,7 @@
         <v>0.24186666666666667</v>
       </c>
       <c r="S94" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="95" spans="16:19" x14ac:dyDescent="0.45">
@@ -22434,7 +22437,7 @@
         <v>0.36306666666666665</v>
       </c>
       <c r="S95" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="96" spans="16:19" x14ac:dyDescent="0.45">
@@ -22448,7 +22451,7 @@
         <v>0.34923333333333334</v>
       </c>
       <c r="S96" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="97" spans="16:19" x14ac:dyDescent="0.45">
@@ -22462,7 +22465,7 @@
         <v>0.25130000000000002</v>
       </c>
       <c r="S97" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="98" spans="16:19" x14ac:dyDescent="0.45">
@@ -22476,7 +22479,7 @@
         <v>0.28016666666666667</v>
       </c>
       <c r="S98" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="99" spans="16:19" x14ac:dyDescent="0.45">
@@ -22490,7 +22493,7 @@
         <v>0.37040000000000001</v>
       </c>
       <c r="S99" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="100" spans="16:19" x14ac:dyDescent="0.45">
@@ -22504,7 +22507,7 @@
         <v>0.32103333333333334</v>
       </c>
       <c r="S100" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="101" spans="16:19" x14ac:dyDescent="0.45">
@@ -22518,7 +22521,7 @@
         <v>0.29316666666666663</v>
       </c>
       <c r="S101" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="102" spans="16:19" x14ac:dyDescent="0.45">
@@ -22532,7 +22535,7 @@
         <v>0.2056</v>
       </c>
       <c r="S102" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="103" spans="16:19" x14ac:dyDescent="0.45">
@@ -22546,7 +22549,7 @@
         <v>0.37253333333333333</v>
       </c>
       <c r="S103" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="104" spans="16:19" x14ac:dyDescent="0.45">
@@ -22560,7 +22563,7 @@
         <v>0.35886666666666667</v>
       </c>
       <c r="S104" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="105" spans="16:19" x14ac:dyDescent="0.45">
@@ -22574,7 +22577,7 @@
         <v>0.30459999999999998</v>
       </c>
       <c r="S105" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="106" spans="16:19" x14ac:dyDescent="0.45">
@@ -22588,7 +22591,7 @@
         <v>0.21409999999999998</v>
       </c>
       <c r="S106" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="107" spans="16:19" x14ac:dyDescent="0.45">
@@ -22602,7 +22605,7 @@
         <v>0.38046666666666668</v>
       </c>
       <c r="S107" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="108" spans="16:19" x14ac:dyDescent="0.45">
@@ -22616,7 +22619,7 @@
         <v>0.40293333333333331</v>
       </c>
       <c r="S108" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="109" spans="16:19" x14ac:dyDescent="0.45">
@@ -22630,7 +22633,7 @@
         <v>0.31109999999999999</v>
       </c>
       <c r="S109" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="110" spans="16:19" x14ac:dyDescent="0.45">
@@ -22644,7 +22647,7 @@
         <v>0.26540000000000002</v>
       </c>
       <c r="S110" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="111" spans="16:19" x14ac:dyDescent="0.45">
@@ -22658,7 +22661,7 @@
         <v>0.32696666666666668</v>
       </c>
       <c r="S111" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="112" spans="16:19" x14ac:dyDescent="0.45">
@@ -22672,7 +22675,7 @@
         <v>0.32516666666666666</v>
       </c>
       <c r="S112" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="113" spans="16:19" x14ac:dyDescent="0.45">
@@ -22686,7 +22689,7 @@
         <v>0.29059999999999997</v>
       </c>
       <c r="S113" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="114" spans="16:19" x14ac:dyDescent="0.45">
@@ -22700,7 +22703,7 @@
         <v>0.18203333333333335</v>
       </c>
       <c r="S114" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="115" spans="16:19" x14ac:dyDescent="0.45">
@@ -22714,7 +22717,7 @@
         <v>0.29153333333333337</v>
       </c>
       <c r="S115" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="116" spans="16:19" x14ac:dyDescent="0.45">
@@ -22728,7 +22731,7 @@
         <v>0.29143333333333327</v>
       </c>
       <c r="S116" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="117" spans="16:19" x14ac:dyDescent="0.45">
@@ -22742,7 +22745,7 @@
         <v>0.20753333333333335</v>
       </c>
       <c r="S117" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="118" spans="16:19" x14ac:dyDescent="0.45">
@@ -22756,7 +22759,7 @@
         <v>0.22473333333333334</v>
       </c>
       <c r="S118" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="119" spans="16:19" x14ac:dyDescent="0.45">
@@ -22770,7 +22773,7 @@
         <v>0.27843333333333331</v>
       </c>
       <c r="S119" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="120" spans="16:19" x14ac:dyDescent="0.45">
@@ -22784,7 +22787,7 @@
         <v>0.30353333333333332</v>
       </c>
       <c r="S120" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="121" spans="16:19" x14ac:dyDescent="0.45">
@@ -22798,7 +22801,7 @@
         <v>0.25676666666666664</v>
       </c>
       <c r="S121" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="122" spans="16:19" x14ac:dyDescent="0.45">
@@ -22812,7 +22815,7 @@
         <v>0.21706666666666666</v>
       </c>
       <c r="S122" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="123" spans="16:19" x14ac:dyDescent="0.45">
@@ -22826,7 +22829,7 @@
         <v>0.31180000000000002</v>
       </c>
       <c r="S123" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="124" spans="16:19" x14ac:dyDescent="0.45">
@@ -22840,7 +22843,7 @@
         <v>0.29100000000000004</v>
       </c>
       <c r="S124" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="125" spans="16:19" x14ac:dyDescent="0.45">
@@ -22854,7 +22857,7 @@
         <v>0.31703333333333333</v>
       </c>
       <c r="S125" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="126" spans="16:19" x14ac:dyDescent="0.45">
@@ -22868,7 +22871,7 @@
         <v>0.19446666666666668</v>
       </c>
       <c r="S126" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_FRA_grids_kan25\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A72B32D-39A2-4794-B454-9A1D55C6AEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC9964FE-52E2-4F5B-9237-7AE809B1D8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -723,13 +723,19 @@
     <t>D</t>
   </si>
   <si>
-    <t>S4aH2,S2aH2,S1aH2,S3aH2</t>
+    <t>S1aH2,S3aH2,S4aH2,S2aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH1,S4aH3,S2aH1,S3aH3,S4aH1,S1aH3,S2aH3,S3aH1</t>
+    <t>S1aH3,S3aH1,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S2aH3</t>
+  </si>
+  <si>
+    <t>elc_buildings</t>
+  </si>
+  <si>
+    <t>elc_industry</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -745,12 +751,6 @@
   </si>
   <si>
     <t>hydro</t>
-  </si>
-  <si>
-    <t>*[_]buildings</t>
-  </si>
-  <si>
-    <t>*[_]industry</t>
   </si>
 </sst>
 </file>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S1aH1,S4aH3,S2aH1,S3aH3,S4aH1,S1aH3,S2aH3,S3aH1</v>
+        <v>S1aH3,S3aH1,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S2aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S4aH2,S2aH2,S1aH2,S3aH2</v>
+        <v>S1aH2,S3aH2,S4aH2,S2aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1452,7 +1452,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99CFE40D-F1D3-4444-B918-578C35B3B0C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA0F064-9F58-4B43-9B62-B62DCE0FF3B8}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1536,7 +1536,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3E21CC-CF7A-4809-ACF7-5D851BAAC06B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09A94DAE-C4A7-4F7F-853F-B5C07EE88B7A}">
   <dimension ref="B9:O370"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13118,7 +13118,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53AB49D6-AA39-4C88-992E-4F9E0A568CAD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C5F4F5-CED3-4F28-B25D-09BD238BE480}">
   <dimension ref="B9:BL85"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20706,12 +20706,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6831029-69F7-412B-B65A-C9262ED3EA6F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6342E25B-88E4-4881-A6A6-B38506C777B9}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="8" max="8" width="12.1328125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="9" spans="1:19" x14ac:dyDescent="0.45">
       <c r="C9" t="str">
@@ -20719,8 +20716,8 @@
         <v>~TFM_DINS-AT</v>
       </c>
       <c r="H9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_INS-AT: cset_set=DEM")</f>
-        <v>~TFM_INS-AT: cset_set=DEM</v>
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>~TFM_DINS-AT</v>
       </c>
       <c r="L9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
@@ -20763,19 +20760,19 @@
         <v>48</v>
       </c>
       <c r="N10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q10" t="s">
         <v>48</v>
       </c>
       <c r="R10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="S10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.45">
@@ -20796,7 +20793,7 @@
         <v>224</v>
       </c>
       <c r="H11" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I11" t="s">
         <v>52</v>
@@ -20820,10 +20817,10 @@
         <v>37</v>
       </c>
       <c r="R11">
-        <v>0.31556666666666672</v>
+        <v>0.31556666666666661</v>
       </c>
       <c r="S11" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.45">
@@ -20840,7 +20837,7 @@
         <v>224</v>
       </c>
       <c r="H12" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I12" t="s">
         <v>54</v>
@@ -20867,7 +20864,7 @@
         <v>0.32903333333333334</v>
       </c>
       <c r="S12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.45">
@@ -20884,7 +20881,7 @@
         <v>224</v>
       </c>
       <c r="H13" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I13" t="s">
         <v>55</v>
@@ -20908,10 +20905,10 @@
         <v>43</v>
       </c>
       <c r="R13">
-        <v>0.2475333333333333</v>
+        <v>0.24753333333333336</v>
       </c>
       <c r="S13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.45">
@@ -20928,7 +20925,7 @@
         <v>224</v>
       </c>
       <c r="H14" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I14" t="s">
         <v>56</v>
@@ -20955,7 +20952,7 @@
         <v>0.21636666666666668</v>
       </c>
       <c r="S14" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.45">
@@ -20972,7 +20969,7 @@
         <v>224</v>
       </c>
       <c r="H15" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I15" t="s">
         <v>57</v>
@@ -20999,7 +20996,7 @@
         <v>0.33883333333333332</v>
       </c>
       <c r="S15" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.45">
@@ -21016,7 +21013,7 @@
         <v>224</v>
       </c>
       <c r="H16" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I16" t="s">
         <v>58</v>
@@ -21043,7 +21040,7 @@
         <v>0.27746666666666669</v>
       </c>
       <c r="S16" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" spans="3:19" x14ac:dyDescent="0.45">
@@ -21060,7 +21057,7 @@
         <v>224</v>
       </c>
       <c r="H17" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I17" t="s">
         <v>59</v>
@@ -21087,7 +21084,7 @@
         <v>0.27649999999999997</v>
       </c>
       <c r="S17" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.45">
@@ -21104,7 +21101,7 @@
         <v>224</v>
       </c>
       <c r="H18" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I18" t="s">
         <v>60</v>
@@ -21131,7 +21128,7 @@
         <v>0.17016666666666666</v>
       </c>
       <c r="S18" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.45">
@@ -21148,7 +21145,7 @@
         <v>224</v>
       </c>
       <c r="H19" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I19" t="s">
         <v>61</v>
@@ -21175,7 +21172,7 @@
         <v>0.25390000000000001</v>
       </c>
       <c r="S19" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.45">
@@ -21192,7 +21189,7 @@
         <v>224</v>
       </c>
       <c r="H20" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I20" t="s">
         <v>62</v>
@@ -21219,7 +21216,7 @@
         <v>0.23780000000000001</v>
       </c>
       <c r="S20" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.45">
@@ -21236,7 +21233,7 @@
         <v>224</v>
       </c>
       <c r="H21" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I21" t="s">
         <v>63</v>
@@ -21260,10 +21257,10 @@
         <v>43</v>
       </c>
       <c r="R21">
-        <v>0.16893333333333335</v>
+        <v>0.1689333333333333</v>
       </c>
       <c r="S21" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" spans="3:19" x14ac:dyDescent="0.45">
@@ -21280,7 +21277,7 @@
         <v>224</v>
       </c>
       <c r="H22" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I22" t="s">
         <v>64</v>
@@ -21307,12 +21304,12 @@
         <v>0.15003333333333332</v>
       </c>
       <c r="S22" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H23" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I23" t="s">
         <v>52</v>
@@ -21330,12 +21327,12 @@
         <v>0.29619999999999996</v>
       </c>
       <c r="S23" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="24" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H24" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I24" t="s">
         <v>54</v>
@@ -21353,12 +21350,12 @@
         <v>0.27356666666666668</v>
       </c>
       <c r="S24" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H25" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I25" t="s">
         <v>55</v>
@@ -21376,12 +21373,12 @@
         <v>0.23003333333333331</v>
       </c>
       <c r="S25" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H26" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I26" t="s">
         <v>56</v>
@@ -21399,12 +21396,12 @@
         <v>0.2056</v>
       </c>
       <c r="S26" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H27" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I27" t="s">
         <v>57</v>
@@ -21422,12 +21419,12 @@
         <v>0.30990000000000001</v>
       </c>
       <c r="S27" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H28" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I28" t="s">
         <v>58</v>
@@ -21445,12 +21442,12 @@
         <v>0.24750000000000003</v>
       </c>
       <c r="S28" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H29" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I29" t="s">
         <v>59</v>
@@ -21465,15 +21462,15 @@
         <v>43</v>
       </c>
       <c r="R29">
-        <v>0.23356666666666667</v>
+        <v>0.23356666666666662</v>
       </c>
       <c r="S29" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H30" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I30" t="s">
         <v>60</v>
@@ -21491,12 +21488,12 @@
         <v>0.18826666666666667</v>
       </c>
       <c r="S30" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H31" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I31" t="s">
         <v>61</v>
@@ -21511,15 +21508,15 @@
         <v>37</v>
       </c>
       <c r="R31">
-        <v>0.30763333333333337</v>
+        <v>0.30763333333333331</v>
       </c>
       <c r="S31" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H32" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I32" t="s">
         <v>62</v>
@@ -21537,12 +21534,12 @@
         <v>0.32896666666666668</v>
       </c>
       <c r="S32" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="33" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H33" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I33" t="s">
         <v>63</v>
@@ -21557,15 +21554,15 @@
         <v>43</v>
       </c>
       <c r="R33">
-        <v>0.23676666666666665</v>
+        <v>0.23676666666666668</v>
       </c>
       <c r="S33" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="34" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H34" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I34" t="s">
         <v>64</v>
@@ -21583,7 +21580,7 @@
         <v>0.20086666666666667</v>
       </c>
       <c r="S34" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="35" spans="8:19" x14ac:dyDescent="0.45">
@@ -21597,7 +21594,7 @@
         <v>0.3652333333333333</v>
       </c>
       <c r="S35" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="36" spans="8:19" x14ac:dyDescent="0.45">
@@ -21608,10 +21605,10 @@
         <v>41</v>
       </c>
       <c r="R36">
-        <v>0.34646666666666665</v>
+        <v>0.3464666666666667</v>
       </c>
       <c r="S36" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="37" spans="8:19" x14ac:dyDescent="0.45">
@@ -21625,7 +21622,7 @@
         <v>0.25796666666666668</v>
       </c>
       <c r="S37" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="38" spans="8:19" x14ac:dyDescent="0.45">
@@ -21639,7 +21636,7 @@
         <v>0.19089999999999999</v>
       </c>
       <c r="S38" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="39" spans="8:19" x14ac:dyDescent="0.45">
@@ -21650,10 +21647,10 @@
         <v>37</v>
       </c>
       <c r="R39">
-        <v>0.31886666666666663</v>
+        <v>0.31886666666666669</v>
       </c>
       <c r="S39" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="40" spans="8:19" x14ac:dyDescent="0.45">
@@ -21667,7 +21664,7 @@
         <v>0.34953333333333331</v>
       </c>
       <c r="S40" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="41" spans="8:19" x14ac:dyDescent="0.45">
@@ -21681,7 +21678,7 @@
         <v>0.24443333333333331</v>
       </c>
       <c r="S41" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="42" spans="8:19" x14ac:dyDescent="0.45">
@@ -21695,7 +21692,7 @@
         <v>0.16983333333333331</v>
       </c>
       <c r="S42" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="43" spans="8:19" x14ac:dyDescent="0.45">
@@ -21709,7 +21706,7 @@
         <v>0.31743333333333335</v>
       </c>
       <c r="S43" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="44" spans="8:19" x14ac:dyDescent="0.45">
@@ -21720,10 +21717,10 @@
         <v>41</v>
       </c>
       <c r="R44">
-        <v>0.36359999999999992</v>
+        <v>0.36359999999999998</v>
       </c>
       <c r="S44" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="45" spans="8:19" x14ac:dyDescent="0.45">
@@ -21737,7 +21734,7 @@
         <v>0.24803333333333333</v>
       </c>
       <c r="S45" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="46" spans="8:19" x14ac:dyDescent="0.45">
@@ -21751,7 +21748,7 @@
         <v>0.20230000000000001</v>
       </c>
       <c r="S46" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="47" spans="8:19" x14ac:dyDescent="0.45">
@@ -21765,7 +21762,7 @@
         <v>0.33770000000000006</v>
       </c>
       <c r="S47" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="48" spans="8:19" x14ac:dyDescent="0.45">
@@ -21779,7 +21776,7 @@
         <v>0.34693333333333332</v>
       </c>
       <c r="S48" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="49" spans="16:19" x14ac:dyDescent="0.45">
@@ -21790,10 +21787,10 @@
         <v>43</v>
       </c>
       <c r="R49">
-        <v>0.2714333333333333</v>
+        <v>0.27143333333333336</v>
       </c>
       <c r="S49" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="50" spans="16:19" x14ac:dyDescent="0.45">
@@ -21807,7 +21804,7 @@
         <v>0.20003333333333337</v>
       </c>
       <c r="S50" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="51" spans="16:19" x14ac:dyDescent="0.45">
@@ -21821,7 +21818,7 @@
         <v>0.2742</v>
       </c>
       <c r="S51" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="52" spans="16:19" x14ac:dyDescent="0.45">
@@ -21832,10 +21829,10 @@
         <v>41</v>
       </c>
       <c r="R52">
-        <v>0.25089999999999996</v>
+        <v>0.25090000000000001</v>
       </c>
       <c r="S52" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="53" spans="16:19" x14ac:dyDescent="0.45">
@@ -21849,7 +21846,7 @@
         <v>0.23026666666666665</v>
       </c>
       <c r="S53" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="54" spans="16:19" x14ac:dyDescent="0.45">
@@ -21863,7 +21860,7 @@
         <v>0.18776666666666667</v>
       </c>
       <c r="S54" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="55" spans="16:19" x14ac:dyDescent="0.45">
@@ -21874,10 +21871,10 @@
         <v>37</v>
       </c>
       <c r="R55">
-        <v>0.30149999999999993</v>
+        <v>0.30149999999999999</v>
       </c>
       <c r="S55" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="56" spans="16:19" x14ac:dyDescent="0.45">
@@ -21888,10 +21885,10 @@
         <v>41</v>
       </c>
       <c r="R56">
-        <v>0.33426666666666666</v>
+        <v>0.33426666666666671</v>
       </c>
       <c r="S56" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="57" spans="16:19" x14ac:dyDescent="0.45">
@@ -21905,7 +21902,7 @@
         <v>0.25666666666666665</v>
       </c>
       <c r="S57" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="58" spans="16:19" x14ac:dyDescent="0.45">
@@ -21919,7 +21916,7 @@
         <v>0.17489999999999997</v>
       </c>
       <c r="S58" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="59" spans="16:19" x14ac:dyDescent="0.45">
@@ -21933,7 +21930,7 @@
         <v>0.27499999999999997</v>
       </c>
       <c r="S59" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="60" spans="16:19" x14ac:dyDescent="0.45">
@@ -21947,7 +21944,7 @@
         <v>0.27550000000000002</v>
       </c>
       <c r="S60" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="61" spans="16:19" x14ac:dyDescent="0.45">
@@ -21961,7 +21958,7 @@
         <v>0.23386666666666667</v>
       </c>
       <c r="S61" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="62" spans="16:19" x14ac:dyDescent="0.45">
@@ -21975,7 +21972,7 @@
         <v>0.15140000000000001</v>
       </c>
       <c r="S62" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="63" spans="16:19" x14ac:dyDescent="0.45">
@@ -21989,7 +21986,7 @@
         <v>0.28456666666666669</v>
       </c>
       <c r="S63" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="64" spans="16:19" x14ac:dyDescent="0.45">
@@ -22003,7 +22000,7 @@
         <v>0.33493333333333331</v>
       </c>
       <c r="S64" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="65" spans="16:19" x14ac:dyDescent="0.45">
@@ -22017,7 +22014,7 @@
         <v>0.25253333333333333</v>
       </c>
       <c r="S65" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="66" spans="16:19" x14ac:dyDescent="0.45">
@@ -22031,7 +22028,7 @@
         <v>0.17956666666666665</v>
       </c>
       <c r="S66" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="67" spans="16:19" x14ac:dyDescent="0.45">
@@ -22045,7 +22042,7 @@
         <v>0.28899999999999998</v>
       </c>
       <c r="S67" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="68" spans="16:19" x14ac:dyDescent="0.45">
@@ -22056,10 +22053,10 @@
         <v>41</v>
       </c>
       <c r="R68">
-        <v>0.29876666666666668</v>
+        <v>0.29876666666666662</v>
       </c>
       <c r="S68" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="69" spans="16:19" x14ac:dyDescent="0.45">
@@ -22073,7 +22070,7 @@
         <v>0.24546666666666669</v>
       </c>
       <c r="S69" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="70" spans="16:19" x14ac:dyDescent="0.45">
@@ -22087,7 +22084,7 @@
         <v>0.1855</v>
       </c>
       <c r="S70" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="71" spans="16:19" x14ac:dyDescent="0.45">
@@ -22101,7 +22098,7 @@
         <v>0.27283333333333332</v>
       </c>
       <c r="S71" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="72" spans="16:19" x14ac:dyDescent="0.45">
@@ -22115,7 +22112,7 @@
         <v>0.27016666666666667</v>
       </c>
       <c r="S72" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="73" spans="16:19" x14ac:dyDescent="0.45">
@@ -22126,10 +22123,10 @@
         <v>43</v>
       </c>
       <c r="R73">
-        <v>0.20276666666666668</v>
+        <v>0.20276666666666665</v>
       </c>
       <c r="S73" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="74" spans="16:19" x14ac:dyDescent="0.45">
@@ -22143,7 +22140,7 @@
         <v>0.1724</v>
       </c>
       <c r="S74" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="75" spans="16:19" x14ac:dyDescent="0.45">
@@ -22154,10 +22151,10 @@
         <v>37</v>
       </c>
       <c r="R75">
-        <v>0.31776666666666664</v>
+        <v>0.3177666666666667</v>
       </c>
       <c r="S75" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="76" spans="16:19" x14ac:dyDescent="0.45">
@@ -22171,7 +22168,7 @@
         <v>0.29699999999999999</v>
       </c>
       <c r="S76" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="77" spans="16:19" x14ac:dyDescent="0.45">
@@ -22182,10 +22179,10 @@
         <v>43</v>
       </c>
       <c r="R77">
-        <v>0.23066666666666669</v>
+        <v>0.23066666666666666</v>
       </c>
       <c r="S77" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="78" spans="16:19" x14ac:dyDescent="0.45">
@@ -22199,7 +22196,7 @@
         <v>0.17943333333333333</v>
       </c>
       <c r="S78" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="79" spans="16:19" x14ac:dyDescent="0.45">
@@ -22213,7 +22210,7 @@
         <v>0.3617333333333333</v>
       </c>
       <c r="S79" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="80" spans="16:19" x14ac:dyDescent="0.45">
@@ -22227,7 +22224,7 @@
         <v>0.29273333333333335</v>
       </c>
       <c r="S80" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="81" spans="16:19" x14ac:dyDescent="0.45">
@@ -22241,7 +22238,7 @@
         <v>0.25616666666666665</v>
       </c>
       <c r="S81" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="82" spans="16:19" x14ac:dyDescent="0.45">
@@ -22255,7 +22252,7 @@
         <v>0.20813333333333331</v>
       </c>
       <c r="S82" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="83" spans="16:19" x14ac:dyDescent="0.45">
@@ -22269,7 +22266,7 @@
         <v>0.38593333333333329</v>
       </c>
       <c r="S83" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="84" spans="16:19" x14ac:dyDescent="0.45">
@@ -22283,7 +22280,7 @@
         <v>0.36663333333333331</v>
       </c>
       <c r="S84" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="85" spans="16:19" x14ac:dyDescent="0.45">
@@ -22297,7 +22294,7 @@
         <v>0.28786666666666666</v>
       </c>
       <c r="S85" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="86" spans="16:19" x14ac:dyDescent="0.45">
@@ -22311,7 +22308,7 @@
         <v>0.23529999999999998</v>
       </c>
       <c r="S86" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="87" spans="16:19" x14ac:dyDescent="0.45">
@@ -22325,7 +22322,7 @@
         <v>0.37480000000000002</v>
       </c>
       <c r="S87" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="88" spans="16:19" x14ac:dyDescent="0.45">
@@ -22339,7 +22336,7 @@
         <v>0.34139999999999998</v>
       </c>
       <c r="S88" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="89" spans="16:19" x14ac:dyDescent="0.45">
@@ -22353,7 +22350,7 @@
         <v>0.2883</v>
       </c>
       <c r="S89" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="90" spans="16:19" x14ac:dyDescent="0.45">
@@ -22367,7 +22364,7 @@
         <v>0.28793333333333332</v>
       </c>
       <c r="S90" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="91" spans="16:19" x14ac:dyDescent="0.45">
@@ -22381,7 +22378,7 @@
         <v>0.41136666666666666</v>
       </c>
       <c r="S91" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="92" spans="16:19" x14ac:dyDescent="0.45">
@@ -22392,10 +22389,10 @@
         <v>41</v>
       </c>
       <c r="R92">
-        <v>0.40083333333333332</v>
+        <v>0.40083333333333337</v>
       </c>
       <c r="S92" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="93" spans="16:19" x14ac:dyDescent="0.45">
@@ -22409,7 +22406,7 @@
         <v>0.31986666666666669</v>
       </c>
       <c r="S93" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="94" spans="16:19" x14ac:dyDescent="0.45">
@@ -22423,7 +22420,7 @@
         <v>0.24186666666666667</v>
       </c>
       <c r="S94" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="95" spans="16:19" x14ac:dyDescent="0.45">
@@ -22437,7 +22434,7 @@
         <v>0.36306666666666665</v>
       </c>
       <c r="S95" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="96" spans="16:19" x14ac:dyDescent="0.45">
@@ -22448,10 +22445,10 @@
         <v>41</v>
       </c>
       <c r="R96">
-        <v>0.34923333333333334</v>
+        <v>0.34923333333333328</v>
       </c>
       <c r="S96" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="97" spans="16:19" x14ac:dyDescent="0.45">
@@ -22465,7 +22462,7 @@
         <v>0.25130000000000002</v>
       </c>
       <c r="S97" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="98" spans="16:19" x14ac:dyDescent="0.45">
@@ -22479,7 +22476,7 @@
         <v>0.28016666666666667</v>
       </c>
       <c r="S98" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="99" spans="16:19" x14ac:dyDescent="0.45">
@@ -22493,7 +22490,7 @@
         <v>0.37040000000000001</v>
       </c>
       <c r="S99" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="100" spans="16:19" x14ac:dyDescent="0.45">
@@ -22507,7 +22504,7 @@
         <v>0.32103333333333334</v>
       </c>
       <c r="S100" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="101" spans="16:19" x14ac:dyDescent="0.45">
@@ -22518,10 +22515,10 @@
         <v>43</v>
       </c>
       <c r="R101">
-        <v>0.29316666666666663</v>
+        <v>0.29316666666666669</v>
       </c>
       <c r="S101" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="102" spans="16:19" x14ac:dyDescent="0.45">
@@ -22535,7 +22532,7 @@
         <v>0.2056</v>
       </c>
       <c r="S102" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="103" spans="16:19" x14ac:dyDescent="0.45">
@@ -22549,7 +22546,7 @@
         <v>0.37253333333333333</v>
       </c>
       <c r="S103" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="104" spans="16:19" x14ac:dyDescent="0.45">
@@ -22563,7 +22560,7 @@
         <v>0.35886666666666667</v>
       </c>
       <c r="S104" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="105" spans="16:19" x14ac:dyDescent="0.45">
@@ -22577,7 +22574,7 @@
         <v>0.30459999999999998</v>
       </c>
       <c r="S105" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="106" spans="16:19" x14ac:dyDescent="0.45">
@@ -22591,7 +22588,7 @@
         <v>0.21409999999999998</v>
       </c>
       <c r="S106" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="107" spans="16:19" x14ac:dyDescent="0.45">
@@ -22605,7 +22602,7 @@
         <v>0.38046666666666668</v>
       </c>
       <c r="S107" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="108" spans="16:19" x14ac:dyDescent="0.45">
@@ -22616,10 +22613,10 @@
         <v>41</v>
       </c>
       <c r="R108">
-        <v>0.40293333333333331</v>
+        <v>0.40293333333333337</v>
       </c>
       <c r="S108" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="109" spans="16:19" x14ac:dyDescent="0.45">
@@ -22633,7 +22630,7 @@
         <v>0.31109999999999999</v>
       </c>
       <c r="S109" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="110" spans="16:19" x14ac:dyDescent="0.45">
@@ -22647,7 +22644,7 @@
         <v>0.26540000000000002</v>
       </c>
       <c r="S110" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="111" spans="16:19" x14ac:dyDescent="0.45">
@@ -22661,7 +22658,7 @@
         <v>0.32696666666666668</v>
       </c>
       <c r="S111" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="112" spans="16:19" x14ac:dyDescent="0.45">
@@ -22675,7 +22672,7 @@
         <v>0.32516666666666666</v>
       </c>
       <c r="S112" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="113" spans="16:19" x14ac:dyDescent="0.45">
@@ -22689,7 +22686,7 @@
         <v>0.29059999999999997</v>
       </c>
       <c r="S113" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="114" spans="16:19" x14ac:dyDescent="0.45">
@@ -22703,7 +22700,7 @@
         <v>0.18203333333333335</v>
       </c>
       <c r="S114" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="115" spans="16:19" x14ac:dyDescent="0.45">
@@ -22717,7 +22714,7 @@
         <v>0.29153333333333337</v>
       </c>
       <c r="S115" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="116" spans="16:19" x14ac:dyDescent="0.45">
@@ -22728,10 +22725,10 @@
         <v>41</v>
       </c>
       <c r="R116">
-        <v>0.29143333333333327</v>
+        <v>0.29143333333333332</v>
       </c>
       <c r="S116" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="117" spans="16:19" x14ac:dyDescent="0.45">
@@ -22745,7 +22742,7 @@
         <v>0.20753333333333335</v>
       </c>
       <c r="S117" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="118" spans="16:19" x14ac:dyDescent="0.45">
@@ -22759,7 +22756,7 @@
         <v>0.22473333333333334</v>
       </c>
       <c r="S118" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="119" spans="16:19" x14ac:dyDescent="0.45">
@@ -22773,7 +22770,7 @@
         <v>0.27843333333333331</v>
       </c>
       <c r="S119" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="120" spans="16:19" x14ac:dyDescent="0.45">
@@ -22784,10 +22781,10 @@
         <v>41</v>
       </c>
       <c r="R120">
-        <v>0.30353333333333332</v>
+        <v>0.30353333333333327</v>
       </c>
       <c r="S120" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="121" spans="16:19" x14ac:dyDescent="0.45">
@@ -22801,7 +22798,7 @@
         <v>0.25676666666666664</v>
       </c>
       <c r="S121" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="122" spans="16:19" x14ac:dyDescent="0.45">
@@ -22815,7 +22812,7 @@
         <v>0.21706666666666666</v>
       </c>
       <c r="S122" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="123" spans="16:19" x14ac:dyDescent="0.45">
@@ -22829,7 +22826,7 @@
         <v>0.31180000000000002</v>
       </c>
       <c r="S123" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="124" spans="16:19" x14ac:dyDescent="0.45">
@@ -22843,7 +22840,7 @@
         <v>0.29100000000000004</v>
       </c>
       <c r="S124" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="125" spans="16:19" x14ac:dyDescent="0.45">
@@ -22857,7 +22854,7 @@
         <v>0.31703333333333333</v>
       </c>
       <c r="S125" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="126" spans="16:19" x14ac:dyDescent="0.45">
@@ -22871,7 +22868,7 @@
         <v>0.19446666666666668</v>
       </c>
       <c r="S126" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC9964FE-52E2-4F5B-9237-7AE809B1D8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E084DB26-4F92-4AC6-85AC-459C0B6BFBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -723,13 +723,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S1aH2,S3aH2,S4aH2,S2aH2</t>
+    <t>S4aH2,S1aH2,S3aH2,S2aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH3,S3aH1,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S2aH3</t>
+    <t>S2aH3,S2aH1,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S1aH3,S3aH1,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S2aH3</v>
+        <v>S2aH3,S2aH1,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S1aH2,S3aH2,S4aH2,S2aH2</v>
+        <v>S4aH2,S1aH2,S3aH2,S2aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1452,7 +1452,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA0F064-9F58-4B43-9B62-B62DCE0FF3B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADFF805B-911D-491B-9175-6C4B9BD21018}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1536,7 +1536,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09A94DAE-C4A7-4F7F-853F-B5C07EE88B7A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FE40C51-FF53-4BD6-B2FC-7E0EC10F59DE}">
   <dimension ref="B9:O370"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13118,7 +13118,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C5F4F5-CED3-4F28-B25D-09BD238BE480}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11225A24-4DF5-4F3C-907D-9F42638FD28D}">
   <dimension ref="B9:BL85"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20706,7 +20706,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6342E25B-88E4-4881-A6A6-B38506C777B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8167ED74-AF0A-488B-A97F-EA0BABD6A105}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20817,7 +20817,7 @@
         <v>37</v>
       </c>
       <c r="R11">
-        <v>0.31556666666666661</v>
+        <v>0.31556666666666672</v>
       </c>
       <c r="S11" t="s">
         <v>236</v>
@@ -21508,7 +21508,7 @@
         <v>37</v>
       </c>
       <c r="R31">
-        <v>0.30763333333333331</v>
+        <v>0.30763333333333337</v>
       </c>
       <c r="S31" t="s">
         <v>236</v>
@@ -21647,7 +21647,7 @@
         <v>37</v>
       </c>
       <c r="R39">
-        <v>0.31886666666666669</v>
+        <v>0.31886666666666663</v>
       </c>
       <c r="S39" t="s">
         <v>236</v>
@@ -21871,7 +21871,7 @@
         <v>37</v>
       </c>
       <c r="R55">
-        <v>0.30149999999999999</v>
+        <v>0.30149999999999993</v>
       </c>
       <c r="S55" t="s">
         <v>236</v>
@@ -22151,7 +22151,7 @@
         <v>37</v>
       </c>
       <c r="R75">
-        <v>0.3177666666666667</v>
+        <v>0.31776666666666664</v>
       </c>
       <c r="S75" t="s">
         <v>236</v>
@@ -22473,7 +22473,7 @@
         <v>45</v>
       </c>
       <c r="R98">
-        <v>0.28016666666666667</v>
+        <v>0.28016666666666662</v>
       </c>
       <c r="S98" t="s">
         <v>236</v>
@@ -22753,7 +22753,7 @@
         <v>45</v>
       </c>
       <c r="R118">
-        <v>0.22473333333333334</v>
+        <v>0.22473333333333331</v>
       </c>
       <c r="S118" t="s">
         <v>236</v>

--- a/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E084DB26-4F92-4AC6-85AC-459C0B6BFBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B854B1-6F87-48A4-A512-186793237121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -732,12 +732,6 @@
     <t>S2aH3,S2aH1,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</t>
   </si>
   <si>
-    <t>elc_buildings</t>
-  </si>
-  <si>
-    <t>elc_industry</t>
-  </si>
-  <si>
     <t>com_pkflx</t>
   </si>
   <si>
@@ -751,6 +745,12 @@
   </si>
   <si>
     <t>hydro</t>
+  </si>
+  <si>
+    <t>*[_]buildings</t>
+  </si>
+  <si>
+    <t>*[_]industry</t>
   </si>
 </sst>
 </file>
@@ -20716,8 +20716,8 @@
         <v>~TFM_DINS-AT</v>
       </c>
       <c r="H9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>~TFM_DINS-AT</v>
+        <f>IF(A11="x","DeActivated","~TFM_INS-AT: pset_set=DEM")</f>
+        <v>~TFM_INS-AT: pset_set=DEM</v>
       </c>
       <c r="L9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
@@ -20760,19 +20760,19 @@
         <v>48</v>
       </c>
       <c r="N10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="P10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Q10" t="s">
         <v>48</v>
       </c>
       <c r="R10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="S10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.45">
@@ -20793,7 +20793,7 @@
         <v>224</v>
       </c>
       <c r="H11" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I11" t="s">
         <v>52</v>
@@ -20820,7 +20820,7 @@
         <v>0.31556666666666672</v>
       </c>
       <c r="S11" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.45">
@@ -20837,7 +20837,7 @@
         <v>224</v>
       </c>
       <c r="H12" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I12" t="s">
         <v>54</v>
@@ -20864,7 +20864,7 @@
         <v>0.32903333333333334</v>
       </c>
       <c r="S12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.45">
@@ -20881,7 +20881,7 @@
         <v>224</v>
       </c>
       <c r="H13" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I13" t="s">
         <v>55</v>
@@ -20908,7 +20908,7 @@
         <v>0.24753333333333336</v>
       </c>
       <c r="S13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.45">
@@ -20925,7 +20925,7 @@
         <v>224</v>
       </c>
       <c r="H14" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I14" t="s">
         <v>56</v>
@@ -20952,7 +20952,7 @@
         <v>0.21636666666666668</v>
       </c>
       <c r="S14" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.45">
@@ -20969,7 +20969,7 @@
         <v>224</v>
       </c>
       <c r="H15" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I15" t="s">
         <v>57</v>
@@ -20996,7 +20996,7 @@
         <v>0.33883333333333332</v>
       </c>
       <c r="S15" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.45">
@@ -21013,7 +21013,7 @@
         <v>224</v>
       </c>
       <c r="H16" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I16" t="s">
         <v>58</v>
@@ -21040,7 +21040,7 @@
         <v>0.27746666666666669</v>
       </c>
       <c r="S16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" spans="3:19" x14ac:dyDescent="0.45">
@@ -21057,7 +21057,7 @@
         <v>224</v>
       </c>
       <c r="H17" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I17" t="s">
         <v>59</v>
@@ -21084,7 +21084,7 @@
         <v>0.27649999999999997</v>
       </c>
       <c r="S17" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.45">
@@ -21101,7 +21101,7 @@
         <v>224</v>
       </c>
       <c r="H18" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I18" t="s">
         <v>60</v>
@@ -21128,7 +21128,7 @@
         <v>0.17016666666666666</v>
       </c>
       <c r="S18" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.45">
@@ -21145,7 +21145,7 @@
         <v>224</v>
       </c>
       <c r="H19" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I19" t="s">
         <v>61</v>
@@ -21172,7 +21172,7 @@
         <v>0.25390000000000001</v>
       </c>
       <c r="S19" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.45">
@@ -21189,7 +21189,7 @@
         <v>224</v>
       </c>
       <c r="H20" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I20" t="s">
         <v>62</v>
@@ -21216,7 +21216,7 @@
         <v>0.23780000000000001</v>
       </c>
       <c r="S20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.45">
@@ -21233,7 +21233,7 @@
         <v>224</v>
       </c>
       <c r="H21" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I21" t="s">
         <v>63</v>
@@ -21260,7 +21260,7 @@
         <v>0.1689333333333333</v>
       </c>
       <c r="S21" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22" spans="3:19" x14ac:dyDescent="0.45">
@@ -21277,7 +21277,7 @@
         <v>224</v>
       </c>
       <c r="H22" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I22" t="s">
         <v>64</v>
@@ -21304,12 +21304,12 @@
         <v>0.15003333333333332</v>
       </c>
       <c r="S22" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H23" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I23" t="s">
         <v>52</v>
@@ -21327,12 +21327,12 @@
         <v>0.29619999999999996</v>
       </c>
       <c r="S23" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H24" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I24" t="s">
         <v>54</v>
@@ -21350,12 +21350,12 @@
         <v>0.27356666666666668</v>
       </c>
       <c r="S24" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H25" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I25" t="s">
         <v>55</v>
@@ -21373,12 +21373,12 @@
         <v>0.23003333333333331</v>
       </c>
       <c r="S25" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H26" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I26" t="s">
         <v>56</v>
@@ -21396,12 +21396,12 @@
         <v>0.2056</v>
       </c>
       <c r="S26" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H27" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I27" t="s">
         <v>57</v>
@@ -21419,12 +21419,12 @@
         <v>0.30990000000000001</v>
       </c>
       <c r="S27" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H28" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I28" t="s">
         <v>58</v>
@@ -21442,12 +21442,12 @@
         <v>0.24750000000000003</v>
       </c>
       <c r="S28" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H29" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I29" t="s">
         <v>59</v>
@@ -21465,12 +21465,12 @@
         <v>0.23356666666666662</v>
       </c>
       <c r="S29" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H30" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I30" t="s">
         <v>60</v>
@@ -21488,12 +21488,12 @@
         <v>0.18826666666666667</v>
       </c>
       <c r="S30" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H31" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I31" t="s">
         <v>61</v>
@@ -21511,12 +21511,12 @@
         <v>0.30763333333333337</v>
       </c>
       <c r="S31" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H32" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I32" t="s">
         <v>62</v>
@@ -21534,12 +21534,12 @@
         <v>0.32896666666666668</v>
       </c>
       <c r="S32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H33" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I33" t="s">
         <v>63</v>
@@ -21557,12 +21557,12 @@
         <v>0.23676666666666668</v>
       </c>
       <c r="S33" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H34" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I34" t="s">
         <v>64</v>
@@ -21580,7 +21580,7 @@
         <v>0.20086666666666667</v>
       </c>
       <c r="S34" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" spans="8:19" x14ac:dyDescent="0.45">
@@ -21594,7 +21594,7 @@
         <v>0.3652333333333333</v>
       </c>
       <c r="S35" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="36" spans="8:19" x14ac:dyDescent="0.45">
@@ -21608,7 +21608,7 @@
         <v>0.3464666666666667</v>
       </c>
       <c r="S36" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37" spans="8:19" x14ac:dyDescent="0.45">
@@ -21622,7 +21622,7 @@
         <v>0.25796666666666668</v>
       </c>
       <c r="S37" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="38" spans="8:19" x14ac:dyDescent="0.45">
@@ -21636,7 +21636,7 @@
         <v>0.19089999999999999</v>
       </c>
       <c r="S38" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39" spans="8:19" x14ac:dyDescent="0.45">
@@ -21650,7 +21650,7 @@
         <v>0.31886666666666663</v>
       </c>
       <c r="S39" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="40" spans="8:19" x14ac:dyDescent="0.45">
@@ -21664,7 +21664,7 @@
         <v>0.34953333333333331</v>
       </c>
       <c r="S40" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="41" spans="8:19" x14ac:dyDescent="0.45">
@@ -21678,7 +21678,7 @@
         <v>0.24443333333333331</v>
       </c>
       <c r="S41" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="42" spans="8:19" x14ac:dyDescent="0.45">
@@ -21692,7 +21692,7 @@
         <v>0.16983333333333331</v>
       </c>
       <c r="S42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43" spans="8:19" x14ac:dyDescent="0.45">
@@ -21706,7 +21706,7 @@
         <v>0.31743333333333335</v>
       </c>
       <c r="S43" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="44" spans="8:19" x14ac:dyDescent="0.45">
@@ -21720,7 +21720,7 @@
         <v>0.36359999999999998</v>
       </c>
       <c r="S44" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="45" spans="8:19" x14ac:dyDescent="0.45">
@@ -21734,7 +21734,7 @@
         <v>0.24803333333333333</v>
       </c>
       <c r="S45" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46" spans="8:19" x14ac:dyDescent="0.45">
@@ -21748,7 +21748,7 @@
         <v>0.20230000000000001</v>
       </c>
       <c r="S46" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="47" spans="8:19" x14ac:dyDescent="0.45">
@@ -21762,7 +21762,7 @@
         <v>0.33770000000000006</v>
       </c>
       <c r="S47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" spans="8:19" x14ac:dyDescent="0.45">
@@ -21776,7 +21776,7 @@
         <v>0.34693333333333332</v>
       </c>
       <c r="S48" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49" spans="16:19" x14ac:dyDescent="0.45">
@@ -21790,7 +21790,7 @@
         <v>0.27143333333333336</v>
       </c>
       <c r="S49" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50" spans="16:19" x14ac:dyDescent="0.45">
@@ -21804,7 +21804,7 @@
         <v>0.20003333333333337</v>
       </c>
       <c r="S50" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" spans="16:19" x14ac:dyDescent="0.45">
@@ -21818,7 +21818,7 @@
         <v>0.2742</v>
       </c>
       <c r="S51" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="52" spans="16:19" x14ac:dyDescent="0.45">
@@ -21832,7 +21832,7 @@
         <v>0.25090000000000001</v>
       </c>
       <c r="S52" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53" spans="16:19" x14ac:dyDescent="0.45">
@@ -21846,7 +21846,7 @@
         <v>0.23026666666666665</v>
       </c>
       <c r="S53" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="54" spans="16:19" x14ac:dyDescent="0.45">
@@ -21860,7 +21860,7 @@
         <v>0.18776666666666667</v>
       </c>
       <c r="S54" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" spans="16:19" x14ac:dyDescent="0.45">
@@ -21874,7 +21874,7 @@
         <v>0.30149999999999993</v>
       </c>
       <c r="S55" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="16:19" x14ac:dyDescent="0.45">
@@ -21888,7 +21888,7 @@
         <v>0.33426666666666671</v>
       </c>
       <c r="S56" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="57" spans="16:19" x14ac:dyDescent="0.45">
@@ -21902,7 +21902,7 @@
         <v>0.25666666666666665</v>
       </c>
       <c r="S57" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="58" spans="16:19" x14ac:dyDescent="0.45">
@@ -21916,7 +21916,7 @@
         <v>0.17489999999999997</v>
       </c>
       <c r="S58" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="59" spans="16:19" x14ac:dyDescent="0.45">
@@ -21930,7 +21930,7 @@
         <v>0.27499999999999997</v>
       </c>
       <c r="S59" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="60" spans="16:19" x14ac:dyDescent="0.45">
@@ -21944,7 +21944,7 @@
         <v>0.27550000000000002</v>
       </c>
       <c r="S60" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="61" spans="16:19" x14ac:dyDescent="0.45">
@@ -21958,7 +21958,7 @@
         <v>0.23386666666666667</v>
       </c>
       <c r="S61" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="62" spans="16:19" x14ac:dyDescent="0.45">
@@ -21972,7 +21972,7 @@
         <v>0.15140000000000001</v>
       </c>
       <c r="S62" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="63" spans="16:19" x14ac:dyDescent="0.45">
@@ -21986,7 +21986,7 @@
         <v>0.28456666666666669</v>
       </c>
       <c r="S63" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="64" spans="16:19" x14ac:dyDescent="0.45">
@@ -22000,7 +22000,7 @@
         <v>0.33493333333333331</v>
       </c>
       <c r="S64" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="65" spans="16:19" x14ac:dyDescent="0.45">
@@ -22014,7 +22014,7 @@
         <v>0.25253333333333333</v>
       </c>
       <c r="S65" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="66" spans="16:19" x14ac:dyDescent="0.45">
@@ -22028,7 +22028,7 @@
         <v>0.17956666666666665</v>
       </c>
       <c r="S66" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="67" spans="16:19" x14ac:dyDescent="0.45">
@@ -22042,7 +22042,7 @@
         <v>0.28899999999999998</v>
       </c>
       <c r="S67" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="68" spans="16:19" x14ac:dyDescent="0.45">
@@ -22056,7 +22056,7 @@
         <v>0.29876666666666662</v>
       </c>
       <c r="S68" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" spans="16:19" x14ac:dyDescent="0.45">
@@ -22070,7 +22070,7 @@
         <v>0.24546666666666669</v>
       </c>
       <c r="S69" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="70" spans="16:19" x14ac:dyDescent="0.45">
@@ -22084,7 +22084,7 @@
         <v>0.1855</v>
       </c>
       <c r="S70" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="71" spans="16:19" x14ac:dyDescent="0.45">
@@ -22098,7 +22098,7 @@
         <v>0.27283333333333332</v>
       </c>
       <c r="S71" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72" spans="16:19" x14ac:dyDescent="0.45">
@@ -22112,7 +22112,7 @@
         <v>0.27016666666666667</v>
       </c>
       <c r="S72" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="73" spans="16:19" x14ac:dyDescent="0.45">
@@ -22126,7 +22126,7 @@
         <v>0.20276666666666665</v>
       </c>
       <c r="S73" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="74" spans="16:19" x14ac:dyDescent="0.45">
@@ -22140,7 +22140,7 @@
         <v>0.1724</v>
       </c>
       <c r="S74" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="75" spans="16:19" x14ac:dyDescent="0.45">
@@ -22154,7 +22154,7 @@
         <v>0.31776666666666664</v>
       </c>
       <c r="S75" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="76" spans="16:19" x14ac:dyDescent="0.45">
@@ -22168,7 +22168,7 @@
         <v>0.29699999999999999</v>
       </c>
       <c r="S76" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" spans="16:19" x14ac:dyDescent="0.45">
@@ -22182,7 +22182,7 @@
         <v>0.23066666666666666</v>
       </c>
       <c r="S77" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="78" spans="16:19" x14ac:dyDescent="0.45">
@@ -22196,7 +22196,7 @@
         <v>0.17943333333333333</v>
       </c>
       <c r="S78" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="79" spans="16:19" x14ac:dyDescent="0.45">
@@ -22210,7 +22210,7 @@
         <v>0.3617333333333333</v>
       </c>
       <c r="S79" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="80" spans="16:19" x14ac:dyDescent="0.45">
@@ -22224,7 +22224,7 @@
         <v>0.29273333333333335</v>
       </c>
       <c r="S80" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="81" spans="16:19" x14ac:dyDescent="0.45">
@@ -22238,7 +22238,7 @@
         <v>0.25616666666666665</v>
       </c>
       <c r="S81" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="82" spans="16:19" x14ac:dyDescent="0.45">
@@ -22252,7 +22252,7 @@
         <v>0.20813333333333331</v>
       </c>
       <c r="S82" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="83" spans="16:19" x14ac:dyDescent="0.45">
@@ -22266,7 +22266,7 @@
         <v>0.38593333333333329</v>
       </c>
       <c r="S83" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="84" spans="16:19" x14ac:dyDescent="0.45">
@@ -22280,7 +22280,7 @@
         <v>0.36663333333333331</v>
       </c>
       <c r="S84" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="85" spans="16:19" x14ac:dyDescent="0.45">
@@ -22294,7 +22294,7 @@
         <v>0.28786666666666666</v>
       </c>
       <c r="S85" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="86" spans="16:19" x14ac:dyDescent="0.45">
@@ -22308,7 +22308,7 @@
         <v>0.23529999999999998</v>
       </c>
       <c r="S86" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="87" spans="16:19" x14ac:dyDescent="0.45">
@@ -22322,7 +22322,7 @@
         <v>0.37480000000000002</v>
       </c>
       <c r="S87" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="88" spans="16:19" x14ac:dyDescent="0.45">
@@ -22336,7 +22336,7 @@
         <v>0.34139999999999998</v>
       </c>
       <c r="S88" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="89" spans="16:19" x14ac:dyDescent="0.45">
@@ -22350,7 +22350,7 @@
         <v>0.2883</v>
       </c>
       <c r="S89" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="90" spans="16:19" x14ac:dyDescent="0.45">
@@ -22364,7 +22364,7 @@
         <v>0.28793333333333332</v>
       </c>
       <c r="S90" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="91" spans="16:19" x14ac:dyDescent="0.45">
@@ -22378,7 +22378,7 @@
         <v>0.41136666666666666</v>
       </c>
       <c r="S91" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="92" spans="16:19" x14ac:dyDescent="0.45">
@@ -22392,7 +22392,7 @@
         <v>0.40083333333333337</v>
       </c>
       <c r="S92" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="93" spans="16:19" x14ac:dyDescent="0.45">
@@ -22406,7 +22406,7 @@
         <v>0.31986666666666669</v>
       </c>
       <c r="S93" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="94" spans="16:19" x14ac:dyDescent="0.45">
@@ -22420,7 +22420,7 @@
         <v>0.24186666666666667</v>
       </c>
       <c r="S94" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="95" spans="16:19" x14ac:dyDescent="0.45">
@@ -22434,7 +22434,7 @@
         <v>0.36306666666666665</v>
       </c>
       <c r="S95" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="96" spans="16:19" x14ac:dyDescent="0.45">
@@ -22448,7 +22448,7 @@
         <v>0.34923333333333328</v>
       </c>
       <c r="S96" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="97" spans="16:19" x14ac:dyDescent="0.45">
@@ -22462,7 +22462,7 @@
         <v>0.25130000000000002</v>
       </c>
       <c r="S97" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="98" spans="16:19" x14ac:dyDescent="0.45">
@@ -22476,7 +22476,7 @@
         <v>0.28016666666666662</v>
       </c>
       <c r="S98" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="99" spans="16:19" x14ac:dyDescent="0.45">
@@ -22490,7 +22490,7 @@
         <v>0.37040000000000001</v>
       </c>
       <c r="S99" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="100" spans="16:19" x14ac:dyDescent="0.45">
@@ -22504,7 +22504,7 @@
         <v>0.32103333333333334</v>
       </c>
       <c r="S100" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="101" spans="16:19" x14ac:dyDescent="0.45">
@@ -22518,7 +22518,7 @@
         <v>0.29316666666666669</v>
       </c>
       <c r="S101" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="102" spans="16:19" x14ac:dyDescent="0.45">
@@ -22532,7 +22532,7 @@
         <v>0.2056</v>
       </c>
       <c r="S102" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="103" spans="16:19" x14ac:dyDescent="0.45">
@@ -22546,7 +22546,7 @@
         <v>0.37253333333333333</v>
       </c>
       <c r="S103" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="104" spans="16:19" x14ac:dyDescent="0.45">
@@ -22560,7 +22560,7 @@
         <v>0.35886666666666667</v>
       </c>
       <c r="S104" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="105" spans="16:19" x14ac:dyDescent="0.45">
@@ -22574,7 +22574,7 @@
         <v>0.30459999999999998</v>
       </c>
       <c r="S105" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="106" spans="16:19" x14ac:dyDescent="0.45">
@@ -22588,7 +22588,7 @@
         <v>0.21409999999999998</v>
       </c>
       <c r="S106" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="107" spans="16:19" x14ac:dyDescent="0.45">
@@ -22602,7 +22602,7 @@
         <v>0.38046666666666668</v>
       </c>
       <c r="S107" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="108" spans="16:19" x14ac:dyDescent="0.45">
@@ -22616,7 +22616,7 @@
         <v>0.40293333333333337</v>
       </c>
       <c r="S108" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="109" spans="16:19" x14ac:dyDescent="0.45">
@@ -22630,7 +22630,7 @@
         <v>0.31109999999999999</v>
       </c>
       <c r="S109" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="110" spans="16:19" x14ac:dyDescent="0.45">
@@ -22644,7 +22644,7 @@
         <v>0.26540000000000002</v>
       </c>
       <c r="S110" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="111" spans="16:19" x14ac:dyDescent="0.45">
@@ -22658,7 +22658,7 @@
         <v>0.32696666666666668</v>
       </c>
       <c r="S111" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="112" spans="16:19" x14ac:dyDescent="0.45">
@@ -22672,7 +22672,7 @@
         <v>0.32516666666666666</v>
       </c>
       <c r="S112" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="113" spans="16:19" x14ac:dyDescent="0.45">
@@ -22686,7 +22686,7 @@
         <v>0.29059999999999997</v>
       </c>
       <c r="S113" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="114" spans="16:19" x14ac:dyDescent="0.45">
@@ -22700,7 +22700,7 @@
         <v>0.18203333333333335</v>
       </c>
       <c r="S114" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="115" spans="16:19" x14ac:dyDescent="0.45">
@@ -22714,7 +22714,7 @@
         <v>0.29153333333333337</v>
       </c>
       <c r="S115" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="116" spans="16:19" x14ac:dyDescent="0.45">
@@ -22728,7 +22728,7 @@
         <v>0.29143333333333332</v>
       </c>
       <c r="S116" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="117" spans="16:19" x14ac:dyDescent="0.45">
@@ -22742,7 +22742,7 @@
         <v>0.20753333333333335</v>
       </c>
       <c r="S117" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="118" spans="16:19" x14ac:dyDescent="0.45">
@@ -22756,7 +22756,7 @@
         <v>0.22473333333333331</v>
       </c>
       <c r="S118" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="119" spans="16:19" x14ac:dyDescent="0.45">
@@ -22770,7 +22770,7 @@
         <v>0.27843333333333331</v>
       </c>
       <c r="S119" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="120" spans="16:19" x14ac:dyDescent="0.45">
@@ -22784,7 +22784,7 @@
         <v>0.30353333333333327</v>
       </c>
       <c r="S120" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="121" spans="16:19" x14ac:dyDescent="0.45">
@@ -22798,7 +22798,7 @@
         <v>0.25676666666666664</v>
       </c>
       <c r="S121" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="122" spans="16:19" x14ac:dyDescent="0.45">
@@ -22812,7 +22812,7 @@
         <v>0.21706666666666666</v>
       </c>
       <c r="S122" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="123" spans="16:19" x14ac:dyDescent="0.45">
@@ -22826,7 +22826,7 @@
         <v>0.31180000000000002</v>
       </c>
       <c r="S123" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="124" spans="16:19" x14ac:dyDescent="0.45">
@@ -22840,7 +22840,7 @@
         <v>0.29100000000000004</v>
       </c>
       <c r="S124" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="125" spans="16:19" x14ac:dyDescent="0.45">
@@ -22854,7 +22854,7 @@
         <v>0.31703333333333333</v>
       </c>
       <c r="S125" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="126" spans="16:19" x14ac:dyDescent="0.45">
@@ -22868,7 +22868,7 @@
         <v>0.19446666666666668</v>
       </c>
       <c r="S126" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B854B1-6F87-48A4-A512-186793237121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{83D7DF60-38FF-4A77-B9BC-A1D3BD8AB207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -723,13 +723,19 @@
     <t>D</t>
   </si>
   <si>
-    <t>S4aH2,S1aH2,S3aH2,S2aH2</t>
+    <t>S4aH2,S2aH2,S3aH2,S1aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH3,S2aH1,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</t>
+    <t>S2aH3,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S1aH3,S3aH1</t>
+  </si>
+  <si>
+    <t>elc_buildings</t>
+  </si>
+  <si>
+    <t>elc_industry</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -745,12 +751,6 @@
   </si>
   <si>
     <t>hydro</t>
-  </si>
-  <si>
-    <t>*[_]buildings</t>
-  </si>
-  <si>
-    <t>*[_]industry</t>
   </si>
 </sst>
 </file>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH3,S2aH1,S1aH3,S3aH3,S4aH1,S1aH1,S4aH3,S3aH1</v>
+        <v>S2aH3,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S1aH3,S3aH1</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S4aH2,S1aH2,S3aH2,S2aH2</v>
+        <v>S4aH2,S2aH2,S3aH2,S1aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1452,7 +1452,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADFF805B-911D-491B-9175-6C4B9BD21018}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4AFA906-5FE5-4D5D-8CB4-D906D0B01E10}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1536,7 +1536,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FE40C51-FF53-4BD6-B2FC-7E0EC10F59DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCE24118-B782-4291-853A-91915EF48551}">
   <dimension ref="B9:O370"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13118,7 +13118,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11225A24-4DF5-4F3C-907D-9F42638FD28D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A72E830-3B8C-41AA-B5C9-7393809BD064}">
   <dimension ref="B9:BL85"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20706,7 +20706,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8167ED74-AF0A-488B-A97F-EA0BABD6A105}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D89CD572-C454-4FC1-BC17-5396129BF275}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20716,8 +20716,8 @@
         <v>~TFM_DINS-AT</v>
       </c>
       <c r="H9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_INS-AT: pset_set=DEM")</f>
-        <v>~TFM_INS-AT: pset_set=DEM</v>
+        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
+        <v>~TFM_DINS-AT</v>
       </c>
       <c r="L9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
@@ -20760,19 +20760,19 @@
         <v>48</v>
       </c>
       <c r="N10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q10" t="s">
         <v>48</v>
       </c>
       <c r="R10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="S10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.45">
@@ -20793,7 +20793,7 @@
         <v>224</v>
       </c>
       <c r="H11" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I11" t="s">
         <v>52</v>
@@ -20817,10 +20817,10 @@
         <v>37</v>
       </c>
       <c r="R11">
-        <v>0.31556666666666672</v>
+        <v>0.31556666666666661</v>
       </c>
       <c r="S11" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.45">
@@ -20837,7 +20837,7 @@
         <v>224</v>
       </c>
       <c r="H12" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I12" t="s">
         <v>54</v>
@@ -20864,7 +20864,7 @@
         <v>0.32903333333333334</v>
       </c>
       <c r="S12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.45">
@@ -20881,7 +20881,7 @@
         <v>224</v>
       </c>
       <c r="H13" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I13" t="s">
         <v>55</v>
@@ -20908,7 +20908,7 @@
         <v>0.24753333333333336</v>
       </c>
       <c r="S13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.45">
@@ -20925,7 +20925,7 @@
         <v>224</v>
       </c>
       <c r="H14" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I14" t="s">
         <v>56</v>
@@ -20952,7 +20952,7 @@
         <v>0.21636666666666668</v>
       </c>
       <c r="S14" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.45">
@@ -20969,7 +20969,7 @@
         <v>224</v>
       </c>
       <c r="H15" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I15" t="s">
         <v>57</v>
@@ -20996,7 +20996,7 @@
         <v>0.33883333333333332</v>
       </c>
       <c r="S15" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.45">
@@ -21013,7 +21013,7 @@
         <v>224</v>
       </c>
       <c r="H16" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I16" t="s">
         <v>58</v>
@@ -21040,7 +21040,7 @@
         <v>0.27746666666666669</v>
       </c>
       <c r="S16" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" spans="3:19" x14ac:dyDescent="0.45">
@@ -21057,7 +21057,7 @@
         <v>224</v>
       </c>
       <c r="H17" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I17" t="s">
         <v>59</v>
@@ -21084,7 +21084,7 @@
         <v>0.27649999999999997</v>
       </c>
       <c r="S17" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.45">
@@ -21101,7 +21101,7 @@
         <v>224</v>
       </c>
       <c r="H18" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I18" t="s">
         <v>60</v>
@@ -21128,7 +21128,7 @@
         <v>0.17016666666666666</v>
       </c>
       <c r="S18" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.45">
@@ -21145,7 +21145,7 @@
         <v>224</v>
       </c>
       <c r="H19" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I19" t="s">
         <v>61</v>
@@ -21172,7 +21172,7 @@
         <v>0.25390000000000001</v>
       </c>
       <c r="S19" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.45">
@@ -21189,7 +21189,7 @@
         <v>224</v>
       </c>
       <c r="H20" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I20" t="s">
         <v>62</v>
@@ -21216,7 +21216,7 @@
         <v>0.23780000000000001</v>
       </c>
       <c r="S20" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.45">
@@ -21233,7 +21233,7 @@
         <v>224</v>
       </c>
       <c r="H21" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I21" t="s">
         <v>63</v>
@@ -21260,7 +21260,7 @@
         <v>0.1689333333333333</v>
       </c>
       <c r="S21" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" spans="3:19" x14ac:dyDescent="0.45">
@@ -21277,7 +21277,7 @@
         <v>224</v>
       </c>
       <c r="H22" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I22" t="s">
         <v>64</v>
@@ -21301,15 +21301,15 @@
         <v>45</v>
       </c>
       <c r="R22">
-        <v>0.15003333333333332</v>
+        <v>0.15003333333333335</v>
       </c>
       <c r="S22" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H23" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I23" t="s">
         <v>52</v>
@@ -21327,12 +21327,12 @@
         <v>0.29619999999999996</v>
       </c>
       <c r="S23" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="24" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H24" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I24" t="s">
         <v>54</v>
@@ -21350,12 +21350,12 @@
         <v>0.27356666666666668</v>
       </c>
       <c r="S24" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H25" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I25" t="s">
         <v>55</v>
@@ -21373,12 +21373,12 @@
         <v>0.23003333333333331</v>
       </c>
       <c r="S25" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H26" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I26" t="s">
         <v>56</v>
@@ -21396,12 +21396,12 @@
         <v>0.2056</v>
       </c>
       <c r="S26" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H27" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I27" t="s">
         <v>57</v>
@@ -21419,12 +21419,12 @@
         <v>0.30990000000000001</v>
       </c>
       <c r="S27" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H28" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I28" t="s">
         <v>58</v>
@@ -21442,12 +21442,12 @@
         <v>0.24750000000000003</v>
       </c>
       <c r="S28" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H29" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I29" t="s">
         <v>59</v>
@@ -21465,12 +21465,12 @@
         <v>0.23356666666666662</v>
       </c>
       <c r="S29" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H30" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I30" t="s">
         <v>60</v>
@@ -21488,12 +21488,12 @@
         <v>0.18826666666666667</v>
       </c>
       <c r="S30" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H31" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I31" t="s">
         <v>61</v>
@@ -21508,15 +21508,15 @@
         <v>37</v>
       </c>
       <c r="R31">
-        <v>0.30763333333333337</v>
+        <v>0.30763333333333331</v>
       </c>
       <c r="S31" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H32" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I32" t="s">
         <v>62</v>
@@ -21534,12 +21534,12 @@
         <v>0.32896666666666668</v>
       </c>
       <c r="S32" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="33" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H33" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I33" t="s">
         <v>63</v>
@@ -21557,12 +21557,12 @@
         <v>0.23676666666666668</v>
       </c>
       <c r="S33" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="34" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H34" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I34" t="s">
         <v>64</v>
@@ -21580,7 +21580,7 @@
         <v>0.20086666666666667</v>
       </c>
       <c r="S34" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="35" spans="8:19" x14ac:dyDescent="0.45">
@@ -21594,7 +21594,7 @@
         <v>0.3652333333333333</v>
       </c>
       <c r="S35" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="36" spans="8:19" x14ac:dyDescent="0.45">
@@ -21608,7 +21608,7 @@
         <v>0.3464666666666667</v>
       </c>
       <c r="S36" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="37" spans="8:19" x14ac:dyDescent="0.45">
@@ -21622,7 +21622,7 @@
         <v>0.25796666666666668</v>
       </c>
       <c r="S37" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="38" spans="8:19" x14ac:dyDescent="0.45">
@@ -21636,7 +21636,7 @@
         <v>0.19089999999999999</v>
       </c>
       <c r="S38" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="39" spans="8:19" x14ac:dyDescent="0.45">
@@ -21647,10 +21647,10 @@
         <v>37</v>
       </c>
       <c r="R39">
-        <v>0.31886666666666663</v>
+        <v>0.31886666666666669</v>
       </c>
       <c r="S39" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="40" spans="8:19" x14ac:dyDescent="0.45">
@@ -21664,7 +21664,7 @@
         <v>0.34953333333333331</v>
       </c>
       <c r="S40" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="41" spans="8:19" x14ac:dyDescent="0.45">
@@ -21678,7 +21678,7 @@
         <v>0.24443333333333331</v>
       </c>
       <c r="S41" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="42" spans="8:19" x14ac:dyDescent="0.45">
@@ -21689,10 +21689,10 @@
         <v>45</v>
       </c>
       <c r="R42">
-        <v>0.16983333333333331</v>
+        <v>0.16983333333333336</v>
       </c>
       <c r="S42" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="43" spans="8:19" x14ac:dyDescent="0.45">
@@ -21706,7 +21706,7 @@
         <v>0.31743333333333335</v>
       </c>
       <c r="S43" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="44" spans="8:19" x14ac:dyDescent="0.45">
@@ -21720,7 +21720,7 @@
         <v>0.36359999999999998</v>
       </c>
       <c r="S44" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="45" spans="8:19" x14ac:dyDescent="0.45">
@@ -21734,7 +21734,7 @@
         <v>0.24803333333333333</v>
       </c>
       <c r="S45" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="46" spans="8:19" x14ac:dyDescent="0.45">
@@ -21748,7 +21748,7 @@
         <v>0.20230000000000001</v>
       </c>
       <c r="S46" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="47" spans="8:19" x14ac:dyDescent="0.45">
@@ -21762,7 +21762,7 @@
         <v>0.33770000000000006</v>
       </c>
       <c r="S47" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="48" spans="8:19" x14ac:dyDescent="0.45">
@@ -21776,7 +21776,7 @@
         <v>0.34693333333333332</v>
       </c>
       <c r="S48" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="49" spans="16:19" x14ac:dyDescent="0.45">
@@ -21790,7 +21790,7 @@
         <v>0.27143333333333336</v>
       </c>
       <c r="S49" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="50" spans="16:19" x14ac:dyDescent="0.45">
@@ -21804,7 +21804,7 @@
         <v>0.20003333333333337</v>
       </c>
       <c r="S50" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="51" spans="16:19" x14ac:dyDescent="0.45">
@@ -21818,7 +21818,7 @@
         <v>0.2742</v>
       </c>
       <c r="S51" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="52" spans="16:19" x14ac:dyDescent="0.45">
@@ -21832,7 +21832,7 @@
         <v>0.25090000000000001</v>
       </c>
       <c r="S52" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="53" spans="16:19" x14ac:dyDescent="0.45">
@@ -21846,7 +21846,7 @@
         <v>0.23026666666666665</v>
       </c>
       <c r="S53" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="54" spans="16:19" x14ac:dyDescent="0.45">
@@ -21857,10 +21857,10 @@
         <v>45</v>
       </c>
       <c r="R54">
-        <v>0.18776666666666667</v>
+        <v>0.18776666666666664</v>
       </c>
       <c r="S54" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="55" spans="16:19" x14ac:dyDescent="0.45">
@@ -21871,10 +21871,10 @@
         <v>37</v>
       </c>
       <c r="R55">
-        <v>0.30149999999999993</v>
+        <v>0.30149999999999999</v>
       </c>
       <c r="S55" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="56" spans="16:19" x14ac:dyDescent="0.45">
@@ -21888,7 +21888,7 @@
         <v>0.33426666666666671</v>
       </c>
       <c r="S56" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="57" spans="16:19" x14ac:dyDescent="0.45">
@@ -21902,7 +21902,7 @@
         <v>0.25666666666666665</v>
       </c>
       <c r="S57" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="58" spans="16:19" x14ac:dyDescent="0.45">
@@ -21916,7 +21916,7 @@
         <v>0.17489999999999997</v>
       </c>
       <c r="S58" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="59" spans="16:19" x14ac:dyDescent="0.45">
@@ -21930,7 +21930,7 @@
         <v>0.27499999999999997</v>
       </c>
       <c r="S59" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="60" spans="16:19" x14ac:dyDescent="0.45">
@@ -21944,7 +21944,7 @@
         <v>0.27550000000000002</v>
       </c>
       <c r="S60" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="61" spans="16:19" x14ac:dyDescent="0.45">
@@ -21958,7 +21958,7 @@
         <v>0.23386666666666667</v>
       </c>
       <c r="S61" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="62" spans="16:19" x14ac:dyDescent="0.45">
@@ -21972,7 +21972,7 @@
         <v>0.15140000000000001</v>
       </c>
       <c r="S62" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="63" spans="16:19" x14ac:dyDescent="0.45">
@@ -21986,7 +21986,7 @@
         <v>0.28456666666666669</v>
       </c>
       <c r="S63" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="64" spans="16:19" x14ac:dyDescent="0.45">
@@ -22000,7 +22000,7 @@
         <v>0.33493333333333331</v>
       </c>
       <c r="S64" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="65" spans="16:19" x14ac:dyDescent="0.45">
@@ -22014,7 +22014,7 @@
         <v>0.25253333333333333</v>
       </c>
       <c r="S65" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="66" spans="16:19" x14ac:dyDescent="0.45">
@@ -22028,7 +22028,7 @@
         <v>0.17956666666666665</v>
       </c>
       <c r="S66" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="67" spans="16:19" x14ac:dyDescent="0.45">
@@ -22042,7 +22042,7 @@
         <v>0.28899999999999998</v>
       </c>
       <c r="S67" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="68" spans="16:19" x14ac:dyDescent="0.45">
@@ -22056,7 +22056,7 @@
         <v>0.29876666666666662</v>
       </c>
       <c r="S68" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="69" spans="16:19" x14ac:dyDescent="0.45">
@@ -22070,7 +22070,7 @@
         <v>0.24546666666666669</v>
       </c>
       <c r="S69" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="70" spans="16:19" x14ac:dyDescent="0.45">
@@ -22084,7 +22084,7 @@
         <v>0.1855</v>
       </c>
       <c r="S70" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="71" spans="16:19" x14ac:dyDescent="0.45">
@@ -22098,7 +22098,7 @@
         <v>0.27283333333333332</v>
       </c>
       <c r="S71" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="72" spans="16:19" x14ac:dyDescent="0.45">
@@ -22112,7 +22112,7 @@
         <v>0.27016666666666667</v>
       </c>
       <c r="S72" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="73" spans="16:19" x14ac:dyDescent="0.45">
@@ -22126,7 +22126,7 @@
         <v>0.20276666666666665</v>
       </c>
       <c r="S73" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="74" spans="16:19" x14ac:dyDescent="0.45">
@@ -22140,7 +22140,7 @@
         <v>0.1724</v>
       </c>
       <c r="S74" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="75" spans="16:19" x14ac:dyDescent="0.45">
@@ -22151,10 +22151,10 @@
         <v>37</v>
       </c>
       <c r="R75">
-        <v>0.31776666666666664</v>
+        <v>0.3177666666666667</v>
       </c>
       <c r="S75" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="76" spans="16:19" x14ac:dyDescent="0.45">
@@ -22168,7 +22168,7 @@
         <v>0.29699999999999999</v>
       </c>
       <c r="S76" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="77" spans="16:19" x14ac:dyDescent="0.45">
@@ -22182,7 +22182,7 @@
         <v>0.23066666666666666</v>
       </c>
       <c r="S77" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="78" spans="16:19" x14ac:dyDescent="0.45">
@@ -22196,7 +22196,7 @@
         <v>0.17943333333333333</v>
       </c>
       <c r="S78" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="79" spans="16:19" x14ac:dyDescent="0.45">
@@ -22210,7 +22210,7 @@
         <v>0.3617333333333333</v>
       </c>
       <c r="S79" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="80" spans="16:19" x14ac:dyDescent="0.45">
@@ -22224,7 +22224,7 @@
         <v>0.29273333333333335</v>
       </c>
       <c r="S80" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="81" spans="16:19" x14ac:dyDescent="0.45">
@@ -22238,7 +22238,7 @@
         <v>0.25616666666666665</v>
       </c>
       <c r="S81" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="82" spans="16:19" x14ac:dyDescent="0.45">
@@ -22252,7 +22252,7 @@
         <v>0.20813333333333331</v>
       </c>
       <c r="S82" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="83" spans="16:19" x14ac:dyDescent="0.45">
@@ -22266,7 +22266,7 @@
         <v>0.38593333333333329</v>
       </c>
       <c r="S83" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="84" spans="16:19" x14ac:dyDescent="0.45">
@@ -22280,7 +22280,7 @@
         <v>0.36663333333333331</v>
       </c>
       <c r="S84" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="85" spans="16:19" x14ac:dyDescent="0.45">
@@ -22294,7 +22294,7 @@
         <v>0.28786666666666666</v>
       </c>
       <c r="S85" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="86" spans="16:19" x14ac:dyDescent="0.45">
@@ -22308,7 +22308,7 @@
         <v>0.23529999999999998</v>
       </c>
       <c r="S86" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="87" spans="16:19" x14ac:dyDescent="0.45">
@@ -22322,7 +22322,7 @@
         <v>0.37480000000000002</v>
       </c>
       <c r="S87" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="88" spans="16:19" x14ac:dyDescent="0.45">
@@ -22336,7 +22336,7 @@
         <v>0.34139999999999998</v>
       </c>
       <c r="S88" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="89" spans="16:19" x14ac:dyDescent="0.45">
@@ -22350,7 +22350,7 @@
         <v>0.2883</v>
       </c>
       <c r="S89" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="90" spans="16:19" x14ac:dyDescent="0.45">
@@ -22364,7 +22364,7 @@
         <v>0.28793333333333332</v>
       </c>
       <c r="S90" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="91" spans="16:19" x14ac:dyDescent="0.45">
@@ -22378,7 +22378,7 @@
         <v>0.41136666666666666</v>
       </c>
       <c r="S91" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="92" spans="16:19" x14ac:dyDescent="0.45">
@@ -22392,7 +22392,7 @@
         <v>0.40083333333333337</v>
       </c>
       <c r="S92" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="93" spans="16:19" x14ac:dyDescent="0.45">
@@ -22406,7 +22406,7 @@
         <v>0.31986666666666669</v>
       </c>
       <c r="S93" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="94" spans="16:19" x14ac:dyDescent="0.45">
@@ -22420,7 +22420,7 @@
         <v>0.24186666666666667</v>
       </c>
       <c r="S94" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="95" spans="16:19" x14ac:dyDescent="0.45">
@@ -22434,7 +22434,7 @@
         <v>0.36306666666666665</v>
       </c>
       <c r="S95" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="96" spans="16:19" x14ac:dyDescent="0.45">
@@ -22448,7 +22448,7 @@
         <v>0.34923333333333328</v>
       </c>
       <c r="S96" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="97" spans="16:19" x14ac:dyDescent="0.45">
@@ -22462,7 +22462,7 @@
         <v>0.25130000000000002</v>
       </c>
       <c r="S97" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="98" spans="16:19" x14ac:dyDescent="0.45">
@@ -22473,10 +22473,10 @@
         <v>45</v>
       </c>
       <c r="R98">
-        <v>0.28016666666666662</v>
+        <v>0.28016666666666667</v>
       </c>
       <c r="S98" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="99" spans="16:19" x14ac:dyDescent="0.45">
@@ -22490,7 +22490,7 @@
         <v>0.37040000000000001</v>
       </c>
       <c r="S99" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="100" spans="16:19" x14ac:dyDescent="0.45">
@@ -22504,7 +22504,7 @@
         <v>0.32103333333333334</v>
       </c>
       <c r="S100" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="101" spans="16:19" x14ac:dyDescent="0.45">
@@ -22518,7 +22518,7 @@
         <v>0.29316666666666669</v>
       </c>
       <c r="S101" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="102" spans="16:19" x14ac:dyDescent="0.45">
@@ -22532,7 +22532,7 @@
         <v>0.2056</v>
       </c>
       <c r="S102" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="103" spans="16:19" x14ac:dyDescent="0.45">
@@ -22546,7 +22546,7 @@
         <v>0.37253333333333333</v>
       </c>
       <c r="S103" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="104" spans="16:19" x14ac:dyDescent="0.45">
@@ -22560,7 +22560,7 @@
         <v>0.35886666666666667</v>
       </c>
       <c r="S104" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="105" spans="16:19" x14ac:dyDescent="0.45">
@@ -22574,7 +22574,7 @@
         <v>0.30459999999999998</v>
       </c>
       <c r="S105" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="106" spans="16:19" x14ac:dyDescent="0.45">
@@ -22585,10 +22585,10 @@
         <v>45</v>
       </c>
       <c r="R106">
-        <v>0.21409999999999998</v>
+        <v>0.21410000000000004</v>
       </c>
       <c r="S106" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="107" spans="16:19" x14ac:dyDescent="0.45">
@@ -22602,7 +22602,7 @@
         <v>0.38046666666666668</v>
       </c>
       <c r="S107" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="108" spans="16:19" x14ac:dyDescent="0.45">
@@ -22616,7 +22616,7 @@
         <v>0.40293333333333337</v>
       </c>
       <c r="S108" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="109" spans="16:19" x14ac:dyDescent="0.45">
@@ -22630,7 +22630,7 @@
         <v>0.31109999999999999</v>
       </c>
       <c r="S109" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="110" spans="16:19" x14ac:dyDescent="0.45">
@@ -22644,7 +22644,7 @@
         <v>0.26540000000000002</v>
       </c>
       <c r="S110" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="111" spans="16:19" x14ac:dyDescent="0.45">
@@ -22658,7 +22658,7 @@
         <v>0.32696666666666668</v>
       </c>
       <c r="S111" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="112" spans="16:19" x14ac:dyDescent="0.45">
@@ -22672,7 +22672,7 @@
         <v>0.32516666666666666</v>
       </c>
       <c r="S112" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="113" spans="16:19" x14ac:dyDescent="0.45">
@@ -22686,7 +22686,7 @@
         <v>0.29059999999999997</v>
       </c>
       <c r="S113" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="114" spans="16:19" x14ac:dyDescent="0.45">
@@ -22700,7 +22700,7 @@
         <v>0.18203333333333335</v>
       </c>
       <c r="S114" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="115" spans="16:19" x14ac:dyDescent="0.45">
@@ -22714,7 +22714,7 @@
         <v>0.29153333333333337</v>
       </c>
       <c r="S115" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="116" spans="16:19" x14ac:dyDescent="0.45">
@@ -22728,7 +22728,7 @@
         <v>0.29143333333333332</v>
       </c>
       <c r="S116" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="117" spans="16:19" x14ac:dyDescent="0.45">
@@ -22742,7 +22742,7 @@
         <v>0.20753333333333335</v>
       </c>
       <c r="S117" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="118" spans="16:19" x14ac:dyDescent="0.45">
@@ -22753,10 +22753,10 @@
         <v>45</v>
       </c>
       <c r="R118">
-        <v>0.22473333333333331</v>
+        <v>0.22473333333333334</v>
       </c>
       <c r="S118" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="119" spans="16:19" x14ac:dyDescent="0.45">
@@ -22770,7 +22770,7 @@
         <v>0.27843333333333331</v>
       </c>
       <c r="S119" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="120" spans="16:19" x14ac:dyDescent="0.45">
@@ -22784,7 +22784,7 @@
         <v>0.30353333333333327</v>
       </c>
       <c r="S120" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="121" spans="16:19" x14ac:dyDescent="0.45">
@@ -22798,7 +22798,7 @@
         <v>0.25676666666666664</v>
       </c>
       <c r="S121" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="122" spans="16:19" x14ac:dyDescent="0.45">
@@ -22812,7 +22812,7 @@
         <v>0.21706666666666666</v>
       </c>
       <c r="S122" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="123" spans="16:19" x14ac:dyDescent="0.45">
@@ -22826,7 +22826,7 @@
         <v>0.31180000000000002</v>
       </c>
       <c r="S123" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="124" spans="16:19" x14ac:dyDescent="0.45">
@@ -22840,7 +22840,7 @@
         <v>0.29100000000000004</v>
       </c>
       <c r="S124" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="125" spans="16:19" x14ac:dyDescent="0.45">
@@ -22854,7 +22854,7 @@
         <v>0.31703333333333333</v>
       </c>
       <c r="S125" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="126" spans="16:19" x14ac:dyDescent="0.45">
@@ -22868,7 +22868,7 @@
         <v>0.19446666666666668</v>
       </c>
       <c r="S126" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83D7DF60-38FF-4A77-B9BC-A1D3BD8AB207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65556411-7F6F-42B2-84F4-A8EE84F0F776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -732,12 +732,6 @@
     <t>S2aH3,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S1aH3,S3aH1</t>
   </si>
   <si>
-    <t>elc_buildings</t>
-  </si>
-  <si>
-    <t>elc_industry</t>
-  </si>
-  <si>
     <t>com_pkflx</t>
   </si>
   <si>
@@ -751,6 +745,12 @@
   </si>
   <si>
     <t>hydro</t>
+  </si>
+  <si>
+    <t>*[_]buildings</t>
+  </si>
+  <si>
+    <t>*[_]industry</t>
   </si>
 </sst>
 </file>
@@ -20716,8 +20716,8 @@
         <v>~TFM_DINS-AT</v>
       </c>
       <c r="H9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
-        <v>~TFM_DINS-AT</v>
+        <f>IF(A11="x","DeActivated","~TFM_INS-AT: cset_set=DEM")</f>
+        <v>~TFM_INS-AT: cset_set=DEM</v>
       </c>
       <c r="L9" t="str">
         <f>IF(A11="x","DeActivated","~TFM_DINS-AT")</f>
@@ -20760,19 +20760,19 @@
         <v>48</v>
       </c>
       <c r="N10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="P10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Q10" t="s">
         <v>48</v>
       </c>
       <c r="R10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="S10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.45">
@@ -20793,7 +20793,7 @@
         <v>224</v>
       </c>
       <c r="H11" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I11" t="s">
         <v>52</v>
@@ -20820,7 +20820,7 @@
         <v>0.31556666666666661</v>
       </c>
       <c r="S11" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.45">
@@ -20837,7 +20837,7 @@
         <v>224</v>
       </c>
       <c r="H12" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I12" t="s">
         <v>54</v>
@@ -20864,7 +20864,7 @@
         <v>0.32903333333333334</v>
       </c>
       <c r="S12" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.45">
@@ -20881,7 +20881,7 @@
         <v>224</v>
       </c>
       <c r="H13" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I13" t="s">
         <v>55</v>
@@ -20908,7 +20908,7 @@
         <v>0.24753333333333336</v>
       </c>
       <c r="S13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.45">
@@ -20925,7 +20925,7 @@
         <v>224</v>
       </c>
       <c r="H14" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I14" t="s">
         <v>56</v>
@@ -20952,7 +20952,7 @@
         <v>0.21636666666666668</v>
       </c>
       <c r="S14" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.45">
@@ -20969,7 +20969,7 @@
         <v>224</v>
       </c>
       <c r="H15" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I15" t="s">
         <v>57</v>
@@ -20996,7 +20996,7 @@
         <v>0.33883333333333332</v>
       </c>
       <c r="S15" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.45">
@@ -21013,7 +21013,7 @@
         <v>224</v>
       </c>
       <c r="H16" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I16" t="s">
         <v>58</v>
@@ -21040,7 +21040,7 @@
         <v>0.27746666666666669</v>
       </c>
       <c r="S16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" spans="3:19" x14ac:dyDescent="0.45">
@@ -21057,7 +21057,7 @@
         <v>224</v>
       </c>
       <c r="H17" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I17" t="s">
         <v>59</v>
@@ -21084,7 +21084,7 @@
         <v>0.27649999999999997</v>
       </c>
       <c r="S17" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.45">
@@ -21101,7 +21101,7 @@
         <v>224</v>
       </c>
       <c r="H18" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I18" t="s">
         <v>60</v>
@@ -21128,7 +21128,7 @@
         <v>0.17016666666666666</v>
       </c>
       <c r="S18" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.45">
@@ -21145,7 +21145,7 @@
         <v>224</v>
       </c>
       <c r="H19" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I19" t="s">
         <v>61</v>
@@ -21172,7 +21172,7 @@
         <v>0.25390000000000001</v>
       </c>
       <c r="S19" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.45">
@@ -21189,7 +21189,7 @@
         <v>224</v>
       </c>
       <c r="H20" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I20" t="s">
         <v>62</v>
@@ -21216,7 +21216,7 @@
         <v>0.23780000000000001</v>
       </c>
       <c r="S20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.45">
@@ -21233,7 +21233,7 @@
         <v>224</v>
       </c>
       <c r="H21" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I21" t="s">
         <v>63</v>
@@ -21260,7 +21260,7 @@
         <v>0.1689333333333333</v>
       </c>
       <c r="S21" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22" spans="3:19" x14ac:dyDescent="0.45">
@@ -21277,7 +21277,7 @@
         <v>224</v>
       </c>
       <c r="H22" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I22" t="s">
         <v>64</v>
@@ -21304,12 +21304,12 @@
         <v>0.15003333333333335</v>
       </c>
       <c r="S22" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H23" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I23" t="s">
         <v>52</v>
@@ -21327,12 +21327,12 @@
         <v>0.29619999999999996</v>
       </c>
       <c r="S23" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H24" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I24" t="s">
         <v>54</v>
@@ -21350,12 +21350,12 @@
         <v>0.27356666666666668</v>
       </c>
       <c r="S24" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H25" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I25" t="s">
         <v>55</v>
@@ -21373,12 +21373,12 @@
         <v>0.23003333333333331</v>
       </c>
       <c r="S25" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H26" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I26" t="s">
         <v>56</v>
@@ -21396,12 +21396,12 @@
         <v>0.2056</v>
       </c>
       <c r="S26" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H27" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I27" t="s">
         <v>57</v>
@@ -21419,12 +21419,12 @@
         <v>0.30990000000000001</v>
       </c>
       <c r="S27" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H28" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I28" t="s">
         <v>58</v>
@@ -21442,12 +21442,12 @@
         <v>0.24750000000000003</v>
       </c>
       <c r="S28" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H29" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I29" t="s">
         <v>59</v>
@@ -21465,12 +21465,12 @@
         <v>0.23356666666666662</v>
       </c>
       <c r="S29" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H30" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I30" t="s">
         <v>60</v>
@@ -21488,12 +21488,12 @@
         <v>0.18826666666666667</v>
       </c>
       <c r="S30" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H31" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I31" t="s">
         <v>61</v>
@@ -21511,12 +21511,12 @@
         <v>0.30763333333333331</v>
       </c>
       <c r="S31" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.45">
       <c r="H32" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I32" t="s">
         <v>62</v>
@@ -21534,12 +21534,12 @@
         <v>0.32896666666666668</v>
       </c>
       <c r="S32" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H33" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I33" t="s">
         <v>63</v>
@@ -21557,12 +21557,12 @@
         <v>0.23676666666666668</v>
       </c>
       <c r="S33" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34" spans="8:19" x14ac:dyDescent="0.45">
       <c r="H34" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I34" t="s">
         <v>64</v>
@@ -21580,7 +21580,7 @@
         <v>0.20086666666666667</v>
       </c>
       <c r="S34" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" spans="8:19" x14ac:dyDescent="0.45">
@@ -21594,7 +21594,7 @@
         <v>0.3652333333333333</v>
       </c>
       <c r="S35" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="36" spans="8:19" x14ac:dyDescent="0.45">
@@ -21608,7 +21608,7 @@
         <v>0.3464666666666667</v>
       </c>
       <c r="S36" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37" spans="8:19" x14ac:dyDescent="0.45">
@@ -21622,7 +21622,7 @@
         <v>0.25796666666666668</v>
       </c>
       <c r="S37" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="38" spans="8:19" x14ac:dyDescent="0.45">
@@ -21636,7 +21636,7 @@
         <v>0.19089999999999999</v>
       </c>
       <c r="S38" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39" spans="8:19" x14ac:dyDescent="0.45">
@@ -21650,7 +21650,7 @@
         <v>0.31886666666666669</v>
       </c>
       <c r="S39" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="40" spans="8:19" x14ac:dyDescent="0.45">
@@ -21664,7 +21664,7 @@
         <v>0.34953333333333331</v>
       </c>
       <c r="S40" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="41" spans="8:19" x14ac:dyDescent="0.45">
@@ -21678,7 +21678,7 @@
         <v>0.24443333333333331</v>
       </c>
       <c r="S41" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="42" spans="8:19" x14ac:dyDescent="0.45">
@@ -21692,7 +21692,7 @@
         <v>0.16983333333333336</v>
       </c>
       <c r="S42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43" spans="8:19" x14ac:dyDescent="0.45">
@@ -21706,7 +21706,7 @@
         <v>0.31743333333333335</v>
       </c>
       <c r="S43" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="44" spans="8:19" x14ac:dyDescent="0.45">
@@ -21720,7 +21720,7 @@
         <v>0.36359999999999998</v>
       </c>
       <c r="S44" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="45" spans="8:19" x14ac:dyDescent="0.45">
@@ -21734,7 +21734,7 @@
         <v>0.24803333333333333</v>
       </c>
       <c r="S45" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46" spans="8:19" x14ac:dyDescent="0.45">
@@ -21748,7 +21748,7 @@
         <v>0.20230000000000001</v>
       </c>
       <c r="S46" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="47" spans="8:19" x14ac:dyDescent="0.45">
@@ -21762,7 +21762,7 @@
         <v>0.33770000000000006</v>
       </c>
       <c r="S47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" spans="8:19" x14ac:dyDescent="0.45">
@@ -21776,7 +21776,7 @@
         <v>0.34693333333333332</v>
       </c>
       <c r="S48" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49" spans="16:19" x14ac:dyDescent="0.45">
@@ -21790,7 +21790,7 @@
         <v>0.27143333333333336</v>
       </c>
       <c r="S49" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50" spans="16:19" x14ac:dyDescent="0.45">
@@ -21804,7 +21804,7 @@
         <v>0.20003333333333337</v>
       </c>
       <c r="S50" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" spans="16:19" x14ac:dyDescent="0.45">
@@ -21818,7 +21818,7 @@
         <v>0.2742</v>
       </c>
       <c r="S51" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="52" spans="16:19" x14ac:dyDescent="0.45">
@@ -21832,7 +21832,7 @@
         <v>0.25090000000000001</v>
       </c>
       <c r="S52" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53" spans="16:19" x14ac:dyDescent="0.45">
@@ -21846,7 +21846,7 @@
         <v>0.23026666666666665</v>
       </c>
       <c r="S53" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="54" spans="16:19" x14ac:dyDescent="0.45">
@@ -21860,7 +21860,7 @@
         <v>0.18776666666666664</v>
       </c>
       <c r="S54" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" spans="16:19" x14ac:dyDescent="0.45">
@@ -21874,7 +21874,7 @@
         <v>0.30149999999999999</v>
       </c>
       <c r="S55" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="16:19" x14ac:dyDescent="0.45">
@@ -21888,7 +21888,7 @@
         <v>0.33426666666666671</v>
       </c>
       <c r="S56" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="57" spans="16:19" x14ac:dyDescent="0.45">
@@ -21902,7 +21902,7 @@
         <v>0.25666666666666665</v>
       </c>
       <c r="S57" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="58" spans="16:19" x14ac:dyDescent="0.45">
@@ -21916,7 +21916,7 @@
         <v>0.17489999999999997</v>
       </c>
       <c r="S58" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="59" spans="16:19" x14ac:dyDescent="0.45">
@@ -21930,7 +21930,7 @@
         <v>0.27499999999999997</v>
       </c>
       <c r="S59" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="60" spans="16:19" x14ac:dyDescent="0.45">
@@ -21944,7 +21944,7 @@
         <v>0.27550000000000002</v>
       </c>
       <c r="S60" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="61" spans="16:19" x14ac:dyDescent="0.45">
@@ -21958,7 +21958,7 @@
         <v>0.23386666666666667</v>
       </c>
       <c r="S61" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="62" spans="16:19" x14ac:dyDescent="0.45">
@@ -21972,7 +21972,7 @@
         <v>0.15140000000000001</v>
       </c>
       <c r="S62" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="63" spans="16:19" x14ac:dyDescent="0.45">
@@ -21986,7 +21986,7 @@
         <v>0.28456666666666669</v>
       </c>
       <c r="S63" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="64" spans="16:19" x14ac:dyDescent="0.45">
@@ -22000,7 +22000,7 @@
         <v>0.33493333333333331</v>
       </c>
       <c r="S64" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="65" spans="16:19" x14ac:dyDescent="0.45">
@@ -22014,7 +22014,7 @@
         <v>0.25253333333333333</v>
       </c>
       <c r="S65" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="66" spans="16:19" x14ac:dyDescent="0.45">
@@ -22028,7 +22028,7 @@
         <v>0.17956666666666665</v>
       </c>
       <c r="S66" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="67" spans="16:19" x14ac:dyDescent="0.45">
@@ -22042,7 +22042,7 @@
         <v>0.28899999999999998</v>
       </c>
       <c r="S67" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="68" spans="16:19" x14ac:dyDescent="0.45">
@@ -22056,7 +22056,7 @@
         <v>0.29876666666666662</v>
       </c>
       <c r="S68" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" spans="16:19" x14ac:dyDescent="0.45">
@@ -22070,7 +22070,7 @@
         <v>0.24546666666666669</v>
       </c>
       <c r="S69" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="70" spans="16:19" x14ac:dyDescent="0.45">
@@ -22084,7 +22084,7 @@
         <v>0.1855</v>
       </c>
       <c r="S70" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="71" spans="16:19" x14ac:dyDescent="0.45">
@@ -22098,7 +22098,7 @@
         <v>0.27283333333333332</v>
       </c>
       <c r="S71" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72" spans="16:19" x14ac:dyDescent="0.45">
@@ -22112,7 +22112,7 @@
         <v>0.27016666666666667</v>
       </c>
       <c r="S72" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="73" spans="16:19" x14ac:dyDescent="0.45">
@@ -22126,7 +22126,7 @@
         <v>0.20276666666666665</v>
       </c>
       <c r="S73" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="74" spans="16:19" x14ac:dyDescent="0.45">
@@ -22140,7 +22140,7 @@
         <v>0.1724</v>
       </c>
       <c r="S74" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="75" spans="16:19" x14ac:dyDescent="0.45">
@@ -22154,7 +22154,7 @@
         <v>0.3177666666666667</v>
       </c>
       <c r="S75" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="76" spans="16:19" x14ac:dyDescent="0.45">
@@ -22168,7 +22168,7 @@
         <v>0.29699999999999999</v>
       </c>
       <c r="S76" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" spans="16:19" x14ac:dyDescent="0.45">
@@ -22182,7 +22182,7 @@
         <v>0.23066666666666666</v>
       </c>
       <c r="S77" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="78" spans="16:19" x14ac:dyDescent="0.45">
@@ -22196,7 +22196,7 @@
         <v>0.17943333333333333</v>
       </c>
       <c r="S78" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="79" spans="16:19" x14ac:dyDescent="0.45">
@@ -22210,7 +22210,7 @@
         <v>0.3617333333333333</v>
       </c>
       <c r="S79" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="80" spans="16:19" x14ac:dyDescent="0.45">
@@ -22224,7 +22224,7 @@
         <v>0.29273333333333335</v>
       </c>
       <c r="S80" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="81" spans="16:19" x14ac:dyDescent="0.45">
@@ -22238,7 +22238,7 @@
         <v>0.25616666666666665</v>
       </c>
       <c r="S81" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="82" spans="16:19" x14ac:dyDescent="0.45">
@@ -22252,7 +22252,7 @@
         <v>0.20813333333333331</v>
       </c>
       <c r="S82" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="83" spans="16:19" x14ac:dyDescent="0.45">
@@ -22266,7 +22266,7 @@
         <v>0.38593333333333329</v>
       </c>
       <c r="S83" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="84" spans="16:19" x14ac:dyDescent="0.45">
@@ -22280,7 +22280,7 @@
         <v>0.36663333333333331</v>
       </c>
       <c r="S84" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="85" spans="16:19" x14ac:dyDescent="0.45">
@@ -22294,7 +22294,7 @@
         <v>0.28786666666666666</v>
       </c>
       <c r="S85" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="86" spans="16:19" x14ac:dyDescent="0.45">
@@ -22308,7 +22308,7 @@
         <v>0.23529999999999998</v>
       </c>
       <c r="S86" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="87" spans="16:19" x14ac:dyDescent="0.45">
@@ -22322,7 +22322,7 @@
         <v>0.37480000000000002</v>
       </c>
       <c r="S87" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="88" spans="16:19" x14ac:dyDescent="0.45">
@@ -22336,7 +22336,7 @@
         <v>0.34139999999999998</v>
       </c>
       <c r="S88" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="89" spans="16:19" x14ac:dyDescent="0.45">
@@ -22350,7 +22350,7 @@
         <v>0.2883</v>
       </c>
       <c r="S89" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="90" spans="16:19" x14ac:dyDescent="0.45">
@@ -22364,7 +22364,7 @@
         <v>0.28793333333333332</v>
       </c>
       <c r="S90" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="91" spans="16:19" x14ac:dyDescent="0.45">
@@ -22378,7 +22378,7 @@
         <v>0.41136666666666666</v>
       </c>
       <c r="S91" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="92" spans="16:19" x14ac:dyDescent="0.45">
@@ -22392,7 +22392,7 @@
         <v>0.40083333333333337</v>
       </c>
       <c r="S92" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="93" spans="16:19" x14ac:dyDescent="0.45">
@@ -22406,7 +22406,7 @@
         <v>0.31986666666666669</v>
       </c>
       <c r="S93" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="94" spans="16:19" x14ac:dyDescent="0.45">
@@ -22420,7 +22420,7 @@
         <v>0.24186666666666667</v>
       </c>
       <c r="S94" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="95" spans="16:19" x14ac:dyDescent="0.45">
@@ -22434,7 +22434,7 @@
         <v>0.36306666666666665</v>
       </c>
       <c r="S95" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="96" spans="16:19" x14ac:dyDescent="0.45">
@@ -22448,7 +22448,7 @@
         <v>0.34923333333333328</v>
       </c>
       <c r="S96" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="97" spans="16:19" x14ac:dyDescent="0.45">
@@ -22462,7 +22462,7 @@
         <v>0.25130000000000002</v>
       </c>
       <c r="S97" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="98" spans="16:19" x14ac:dyDescent="0.45">
@@ -22476,7 +22476,7 @@
         <v>0.28016666666666667</v>
       </c>
       <c r="S98" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="99" spans="16:19" x14ac:dyDescent="0.45">
@@ -22490,7 +22490,7 @@
         <v>0.37040000000000001</v>
       </c>
       <c r="S99" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="100" spans="16:19" x14ac:dyDescent="0.45">
@@ -22504,7 +22504,7 @@
         <v>0.32103333333333334</v>
       </c>
       <c r="S100" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="101" spans="16:19" x14ac:dyDescent="0.45">
@@ -22518,7 +22518,7 @@
         <v>0.29316666666666669</v>
       </c>
       <c r="S101" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="102" spans="16:19" x14ac:dyDescent="0.45">
@@ -22532,7 +22532,7 @@
         <v>0.2056</v>
       </c>
       <c r="S102" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="103" spans="16:19" x14ac:dyDescent="0.45">
@@ -22546,7 +22546,7 @@
         <v>0.37253333333333333</v>
       </c>
       <c r="S103" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="104" spans="16:19" x14ac:dyDescent="0.45">
@@ -22560,7 +22560,7 @@
         <v>0.35886666666666667</v>
       </c>
       <c r="S104" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="105" spans="16:19" x14ac:dyDescent="0.45">
@@ -22574,7 +22574,7 @@
         <v>0.30459999999999998</v>
       </c>
       <c r="S105" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="106" spans="16:19" x14ac:dyDescent="0.45">
@@ -22588,7 +22588,7 @@
         <v>0.21410000000000004</v>
       </c>
       <c r="S106" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="107" spans="16:19" x14ac:dyDescent="0.45">
@@ -22602,7 +22602,7 @@
         <v>0.38046666666666668</v>
       </c>
       <c r="S107" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="108" spans="16:19" x14ac:dyDescent="0.45">
@@ -22616,7 +22616,7 @@
         <v>0.40293333333333337</v>
       </c>
       <c r="S108" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="109" spans="16:19" x14ac:dyDescent="0.45">
@@ -22630,7 +22630,7 @@
         <v>0.31109999999999999</v>
       </c>
       <c r="S109" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="110" spans="16:19" x14ac:dyDescent="0.45">
@@ -22644,7 +22644,7 @@
         <v>0.26540000000000002</v>
       </c>
       <c r="S110" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="111" spans="16:19" x14ac:dyDescent="0.45">
@@ -22658,7 +22658,7 @@
         <v>0.32696666666666668</v>
       </c>
       <c r="S111" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="112" spans="16:19" x14ac:dyDescent="0.45">
@@ -22672,7 +22672,7 @@
         <v>0.32516666666666666</v>
       </c>
       <c r="S112" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="113" spans="16:19" x14ac:dyDescent="0.45">
@@ -22686,7 +22686,7 @@
         <v>0.29059999999999997</v>
       </c>
       <c r="S113" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="114" spans="16:19" x14ac:dyDescent="0.45">
@@ -22700,7 +22700,7 @@
         <v>0.18203333333333335</v>
       </c>
       <c r="S114" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="115" spans="16:19" x14ac:dyDescent="0.45">
@@ -22714,7 +22714,7 @@
         <v>0.29153333333333337</v>
       </c>
       <c r="S115" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="116" spans="16:19" x14ac:dyDescent="0.45">
@@ -22728,7 +22728,7 @@
         <v>0.29143333333333332</v>
       </c>
       <c r="S116" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="117" spans="16:19" x14ac:dyDescent="0.45">
@@ -22742,7 +22742,7 @@
         <v>0.20753333333333335</v>
       </c>
       <c r="S117" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="118" spans="16:19" x14ac:dyDescent="0.45">
@@ -22756,7 +22756,7 @@
         <v>0.22473333333333334</v>
       </c>
       <c r="S118" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="119" spans="16:19" x14ac:dyDescent="0.45">
@@ -22770,7 +22770,7 @@
         <v>0.27843333333333331</v>
       </c>
       <c r="S119" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="120" spans="16:19" x14ac:dyDescent="0.45">
@@ -22784,7 +22784,7 @@
         <v>0.30353333333333327</v>
       </c>
       <c r="S120" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="121" spans="16:19" x14ac:dyDescent="0.45">
@@ -22798,7 +22798,7 @@
         <v>0.25676666666666664</v>
       </c>
       <c r="S121" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="122" spans="16:19" x14ac:dyDescent="0.45">
@@ -22812,7 +22812,7 @@
         <v>0.21706666666666666</v>
       </c>
       <c r="S122" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="123" spans="16:19" x14ac:dyDescent="0.45">
@@ -22826,7 +22826,7 @@
         <v>0.31180000000000002</v>
       </c>
       <c r="S123" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="124" spans="16:19" x14ac:dyDescent="0.45">
@@ -22840,7 +22840,7 @@
         <v>0.29100000000000004</v>
       </c>
       <c r="S124" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="125" spans="16:19" x14ac:dyDescent="0.45">
@@ -22854,7 +22854,7 @@
         <v>0.31703333333333333</v>
       </c>
       <c r="S125" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="126" spans="16:19" x14ac:dyDescent="0.45">
@@ -22868,7 +22868,7 @@
         <v>0.19446666666666668</v>
       </c>
       <c r="S126" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
